--- a/曼谷自由行心願清單.xlsx
+++ b/曼谷自由行心願清單.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,7 +31,7 @@
       <name val="微軟正黑體"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="微軟正黑體"/>
@@ -54,6 +54,12 @@
     <font>
       <name val="微軟正黑體"/>
       <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <b val="1"/>
+      <color rgb="001B4F72"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -115,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -130,6 +136,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,7 +237,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -253,7 +262,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>3</row>
       <rowOff>0</rowOff>
@@ -278,7 +287,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>4</row>
       <rowOff>0</rowOff>
@@ -303,7 +312,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>5</row>
       <rowOff>0</rowOff>
@@ -328,7 +337,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>6</row>
       <rowOff>0</rowOff>
@@ -353,7 +362,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>7</row>
       <rowOff>0</rowOff>
@@ -378,7 +387,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>8</row>
       <rowOff>0</rowOff>
@@ -403,7 +412,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>9</row>
       <rowOff>0</rowOff>
@@ -428,7 +437,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
@@ -453,7 +462,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>11</row>
       <rowOff>0</rowOff>
@@ -478,7 +487,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>12</row>
       <rowOff>0</rowOff>
@@ -503,7 +512,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>13</row>
       <rowOff>0</rowOff>
@@ -528,7 +537,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>14</row>
       <rowOff>0</rowOff>
@@ -553,7 +562,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>15</row>
       <rowOff>0</rowOff>
@@ -578,7 +587,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>16</row>
       <rowOff>0</rowOff>
@@ -603,7 +612,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>17</row>
       <rowOff>0</rowOff>
@@ -628,7 +637,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>18</row>
       <rowOff>0</rowOff>
@@ -653,7 +662,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>19</row>
       <rowOff>0</rowOff>
@@ -678,7 +687,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>20</row>
       <rowOff>0</rowOff>
@@ -703,7 +712,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>21</row>
       <rowOff>0</rowOff>
@@ -728,7 +737,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>22</row>
       <rowOff>0</rowOff>
@@ -753,7 +762,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>23</row>
       <rowOff>0</rowOff>
@@ -778,7 +787,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>24</row>
       <rowOff>0</rowOff>
@@ -803,7 +812,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>25</row>
       <rowOff>0</rowOff>
@@ -828,7 +837,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>26</row>
       <rowOff>0</rowOff>
@@ -853,7 +862,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>27</row>
       <rowOff>0</rowOff>
@@ -878,7 +887,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>28</row>
       <rowOff>0</rowOff>
@@ -903,7 +912,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>29</row>
       <rowOff>0</rowOff>
@@ -1218,15 +1227,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -1259,10 +1269,15 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>行程標記</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>備註</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>圖片</t>
         </is>
@@ -1291,10 +1306,15 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>🍑Mo 提起，暫定 11/25 首日晚餐。超大峇里島度假風海邊景觀餐廳，建議先 KKday 線上訂位。</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr"/>
+          <t>★ 暫定 11/25 (三) 晚餐</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>超大峇里島度假風海邊景觀餐廳，坐擁無敵海景夕陽，餐點豐富好拍照，建議提前透過 KKday 預訂海景席位。</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr"/>
     </row>
     <row r="4" ht="70" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -1319,10 +1339,15 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>🍑Mo 提起。皇家懸崖海景鳥巢包廂，俯瞰海灣夕陽，採現場排隊候位建議提早抵達。</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr"/>
+          <t>★ 暫定 11/26 (四) 傍晚候選</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>皇家懸崖海景鳥巢包廂，俯瞰海灣日落晚霞極美，採現場排隊候位建議提早前往卡位。</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr"/>
     </row>
     <row r="5" ht="70" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1347,10 +1372,15 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>🍑Mo 提起「下午去特別美」。沙灘藍色懶骨頭席位，波西米亞度假風海灘餐廳，11/27 沙灘日候選。</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr"/>
+          <t>★ 暫定 11/27 (五) 沙灘日候選</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>沙灘藍色懶骨頭席位，波西米亞度假風海灘餐廳，午後至日落時分光線最柔和舒適。</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr"/>
     </row>
     <row r="6" ht="70" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -1375,10 +1405,15 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>🍑Mo 與 芊芊🦄 熱推！中天海灘 38 樓高空酒吧，巨大女王頭燈光秀超好出片，建議預訂景觀席。</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr"/>
+          <t>★ 暫定 11/26 (四) 晚間候選</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>中天海灘第一排 38 樓高空酒吧，招牌巨大女王頭燈光秀極具迷幻高級感，建議提前預訂景觀席位。</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="70" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -1403,10 +1438,15 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>🍑Mo 提起。當地人常去的露天音樂花園酒吧，每晚 Live 樂團現場演出，消費平價親民。</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr"/>
+          <t>★ 暫定 11/27 (五) 晚間候選</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>當地人常去的露天音樂花園酒吧，每晚有現場 Live 樂團演出，氣氛輕鬆熱鬧且消費平價親民。</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr"/>
     </row>
     <row r="8" ht="70" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -1429,12 +1469,17 @@
           <t>09:30 - 18:30</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>🍑Mo 提起。海景落地大窗，主打正宗土耳其高溫熱沙萃取手沖咖啡與千層蛋糕。</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>海景第一排大片落地窗，主打正宗土耳其高溫熱沙萃取手沖咖啡與千層蛋糕，環境文藝放鬆。</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr"/>
     </row>
     <row r="9" ht="70" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -1457,12 +1502,17 @@
           <t>17:00 - 00:00 (建議 17:30 抵達卡位)</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>芊芊🦄 推薦。T-One 大樓 46 樓阿凡達發光水母神樹酒吧，現場候位需備護照查驗（滿 20 歲）。</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>T-One 大樓 46 樓阿凡達發光水母神樹酒吧，360 度俯瞰都會天際線，現場排隊需出示護照查驗（滿 20 歲）。</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr"/>
     </row>
     <row r="10" ht="70" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -1485,12 +1535,17 @@
           <t>11:30 - 14:30 / 17:00 - 01:00</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>芊芊🦄 熱推「超讚約起來」！帝國大廈 56 樓米其林名廚 Ton 打造最高泰式景觀餐廳，需提早訂位。</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>帝國大廈 56 樓米其林名廚 Ton 打造最高泰式景觀餐廳，視野極佳，需提早於官方線上系統訂位。</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr"/>
     </row>
     <row r="11" ht="70" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -1513,12 +1568,17 @@
           <t>10:00 - 21:00</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>丁 推薦。水上小馬爾地夫漂浮泡泡涼亭，車程約 45 分鐘建議包車前往，需提早線上預訂涼亭席位。</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>水上小馬爾地夫漂浮泡泡涼亭，車程約 45 分鐘建議包車前往，需提早線上預訂水上席位。</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr"/>
     </row>
     <row r="12" ht="70" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -1541,12 +1601,17 @@
           <t>11:00 - 01:00</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Emsphere 5 樓商場頂樓星光海灘空中俱樂部，設有無邊際泳池、棕櫚躺椅與音樂 DJ 派對。</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr"/>
     </row>
     <row r="13" ht="70" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -1571,10 +1636,15 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Jerry &amp; 芊芊🦄 推薦，暫定 11/26 半日遊。親手調配草料餵食、大象泥漿浴與溪水刷背，含接送需備換洗衣物。</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr"/>
+          <t>★ 暫定 11/26 (四) 中午半日遊</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>國際生態友善大象保護營，親手調配草料餵食、大象泥漿浴與溪水刷背，含飯店接送需自備換洗衣物。</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr"/>
     </row>
     <row r="14" ht="70" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -1597,12 +1667,17 @@
           <t>14:00 - 21:30</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>🍑Mo 稱「超貴牛逼網美遊艇」，芊芊貼 KKday 609706。外海大型奢華漂浮遊艇俱樂部，Bali Hai 碼頭快艇接駁。</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>外海大型奢華海上漂浮俱樂部遊艇，設有無邊際泳池與 DJ，由 Bali Hai 碼頭搭快艇接駁，KKday 609706。</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr"/>
     </row>
     <row r="15" ht="70" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -1625,12 +1700,17 @@
           <t>08:00 - 18:00 (夕陽場 16:30 最美)</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>🍑Mo 提起「傳統寺廟 夕陽漂亮」。世界最大純木雕手工城堡，臨海峭壁氣勢磅礡，需著過肩過膝服裝。</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>世界最大純木雕手工城堡寺廟，臨海峭壁氣勢磅礡，參觀需著過肩過膝服裝，建議提前線上預約門票。</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr"/>
     </row>
     <row r="16" ht="70" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -1655,10 +1735,15 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>🍑Mo 推薦「男模郵輪地址」。出海賞夕陽、海鮮百匯晚宴、熱情男模秀舞互動與釣魷魚，氣氛極嗨。</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr"/>
+          <t>★ 暫定 11/27 (五) 傍晚候選</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>出海賞夕陽海景、享用海鮮百匯晚宴、熱情男模秀舞互動與夜釣魷魚體驗，氣氛熱烈需提前購票。</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr"/>
     </row>
     <row r="17" ht="70" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -1681,12 +1766,17 @@
           <t>09:00 - 18:00</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>芊芊🦄 提起，Jerry 提醒評價兩極，群組共識先以其他為主，列為彈性備選。需穿耐髒衣鞋。</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>山區越野沙灘車冒險，穿越泥坑與山林小徑，體驗刺激但泥濘度高，建議視時間與體力彈性安排。</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr"/>
     </row>
     <row r="18" ht="70" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -1709,12 +1799,17 @@
           <t>晚餐航行 19:00 - 21:30</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>芊芊🦄 推薦「曼谷浪漫游船」。大型三層豪華客輪，夜賞鄭王廟大皇宮點燈，享海鮮自助餐與爵士樂，River City 登船。</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr"/>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>大型三層豪華客輪，夜賞鄭王廟大皇宮點燈，享海鮮自助餐與爵士樂演奏，於 River City 碼頭登船。</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr"/>
     </row>
     <row r="19" ht="70" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -1737,12 +1832,17 @@
           <t>10:00 - 22:00</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>芊芊🦄 推薦「星羅 6 大重點」！室內冷氣水上市場 SOOKSIAM 品嚐平價小吃、室內瀑布、POP MART 與河畔夜景。</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>一樓冷氣室內水上市場 SOOKSIAM 品嚐平價特色小吃、室內巨型瀑布、POP MART 與河畔水舞夜景。</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr"/>
     </row>
     <row r="20" ht="70" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
@@ -1765,12 +1865,17 @@
           <t>10:00 - 18:00 (傍晚梯次為主)</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>芊芊🦄 推薦。鱷魚頭百年水上老街木屋咖啡館，搭乘木船由親人店貓陪同遊古運河，近 BKK 機場，需私訊預約。</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>鱷魚頭百年水上老街木屋咖啡館，搭乘木舟由親人店貓陪同遊古運河，近 BKK 機場，每日限量需私訊預約。</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr"/>
     </row>
     <row r="21" ht="70" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -1793,12 +1898,17 @@
           <t>21:00 - 02:00 (22:30 大秀最熱鬧)</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>曼谷知名同志夜店猛男秀，舞台聲光震撼，每晚猛男歌舞狂歡大秀，需攜帶護照正本查驗（滿 20 歲）。</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>知名大型同志夜店猛男秀，舞台聲光效果震撼，每晚有猛男歌舞大秀，需攜帶護照正本查驗（滿 20 歲）。</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr"/>
     </row>
     <row r="22" ht="70" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -1823,10 +1933,15 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>🍑Mo 讚「希望能成😍😍😍」、芊芊「超喜歡」！純白極簡 24 樓頂樓高空無邊際泳池，房內附洗脫烘衣機。</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr"/>
+          <t>★ 暫定 11/25~11/27 住宿候選</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>純白極簡現代五星飯店，24 樓頂樓高空無邊際泳池採光極佳，房內附洗脫烘衣機，性價比出眾。</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr"/>
     </row>
     <row r="23" ht="70" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -1851,10 +1966,15 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Jerry 提起「表哥推薦的住宿？」。老牌奢華海濱度假村，坐擁雙私人沙灘與超大花園泳池，悠閒放鬆。</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr"/>
+          <t>★ 暫定 11/25~11/27 住宿候選</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>老牌五星海濱度假村，坐擁兩座專屬私人沙灘與超大熱帶花園泳池，環境開闊靜謐，適合純休閒放鬆。</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr"/>
     </row>
     <row r="24" ht="70" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -1877,12 +1997,17 @@
           <t>入住 15:00 / 退房 12:00</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>🍑Mo 評價「泳池很頂住宿普通」。近 Terminal 21 購物中心，頂樓設有高空無邊際透明泳池與酒吧。</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>近 Terminal 21 購物中心生活機能便利，頂樓設有景觀無邊際透明泳池與酒吧，房間實用標準。</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr"/>
     </row>
     <row r="25" ht="70" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -1905,12 +2030,17 @@
           <t>24 小時完整住滿制</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>🍑Mo 推薦別墅自帶泳池（每人4000多），Jerry與Johnny認太南邊偏遠列備選。享 24 小時住滿制服務。</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>隱世海灘度假村，獨棟別墅自帶私人泳池，享有 24 小時住滿退房制，位置較南端偏遠適合全包式度假。</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr"/>
     </row>
     <row r="26" ht="70" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -1933,12 +2063,17 @@
           <t>入住 15:00 / 退房 12:00</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>IG 推薦。最高大樓 Mahanakhon 內部，西班牙大師圓弧大膽配色設計，房客可免費上 78 樓觀景台。</t>
-        </is>
-      </c>
-      <c r="F26" s="7" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>曼谷最高大樓 Mahanakhon 內部，西班牙大師圓弧大膽撞色設計，房客可免費登上 78 樓 Sky Beach 觀景台。</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr"/>
     </row>
     <row r="27" ht="70" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -1961,12 +2096,17 @@
           <t>入住 14:00 / 退房 12:00</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>對話推薦。阿里文青工業風旅宿，中庭粉嫩 Baby Bar 泳池酒吧超像《模擬市民》場景，周邊咖啡廳林立。</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>阿里文青工業風旅宿，中庭粉嫩 Baby Bar 泳池酒吧宛如《模擬市民》場景，周邊文青咖啡廳林立。</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr"/>
     </row>
     <row r="28" ht="70" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
@@ -1989,12 +2129,17 @@
           <t>入住 15:00 / 退房 12:00</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>丁 推薦「專車接送 離通羅站10分鐘經過7-11與小攤販 有露天泳池」。公寓寬敞附廚房洗烘，生活機能極佳。</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>通羅靜巷質感公寓式飯店，高爾夫球車接駁通羅站，附露天泳池與小廚房洗烘，出巷口有 7-11 與小吃攤。</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr"/>
     </row>
     <row r="29" ht="70" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -2017,12 +2162,17 @@
           <t>入住 15:00 / 退房 12:00</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>對話評「真漂亮但有夠貴」。希爾頓頂級 Curio 精選，標誌性高空朱紅色浪漫無邊際泳池，前衛奢華美學。</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>希爾頓旗下頂級 Curio 精選品牌，標誌性高空朱紅色浪漫無邊際天際泳池，設計前衛大膽，定價偏奢華。</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr"/>
     </row>
     <row r="30" ht="70" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
@@ -2045,16 +2195,21 @@
           <t>入住 15:00 / 退房 12:00</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>舊城區活力設計酒店，綠意中庭天井泳池，步行可達考山路、大皇宮與百年老城街頭米其林美食。</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
@@ -2097,22 +2252,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🗓️ 11/25 - 12/1 泰國曼谷・芭達雅 7天6夜暫定行程規劃表</t>
+          <t>🗓️ 11/25 - 11/27 芭達雅自由行 暫定計畫行程表</t>
         </is>
       </c>
     </row>
@@ -2154,112 +2309,109 @@
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>🌟 啟程日：抵達曼谷機場 ➔ 芭達雅入住 ➔ 峇里島風夕陽晚餐 ➔ 步行街夜市</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="9" t="n"/>
-      <c r="F3" s="9" t="n"/>
-      <c r="G3" s="9" t="n"/>
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>🌟 11/25 (週三) 機場前往芭達雅 ➔ 飯店入住 ➔ 峇里島風夕陽晚餐 ➔ 夜市/步行街</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Day 1
-11/25 (週三)</t>
+          <t>11/25 (週三)</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>12:00 - 15:00</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>抵達曼谷機場 ➔ 專車包車前往芭達雅</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>曼谷機場 (BKK/DMK) ➔ 芭達雅</t>
+          <t>下午時段</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>（1）機場到芭達雅 3 小時</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>曼谷機場 ➔ 芭達雅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>跨城高速公路</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>預約專車包車 (約 2.5~3 小時)</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>🍑Mo 提議第一天先包車直奔芭達雅；建議提前預約 7~9 人座專車接機。</t>
+          <t>跨城交通</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>包車直達 (約 2.5~3 小時)</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>建議提前研究並預訂來回包車接送。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Day 1
-11/25 (週三)</t>
+          <t>11/25 (週三)</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>15:00 - 16:30</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>飯店辦理 Check-in &amp; 放行李梳洗</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Arbour Hotel / Dusit Thani</t>
+          <t>抵達後</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>（2）先去 Check-in</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>芭達雅預定飯店 (如 Arbour Hotel / Dusit Thani)</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>芭達雅市區 / 北區</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
+          <t>芭達雅市區</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>專車抵達</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>群組首選：Arbour Hotel（網美高空無邊際泳池）或 Dusit Thani（表哥推薦度假酒店）。</t>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>辦理入住手續放行李梳洗。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Day 1
-11/25 (週三)</t>
+          <t>11/25 (週三)</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>17:00 - 19:30</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>【夕陽晚餐】The Oxygen 峇里島海景餐廳</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+          <t>傍晚 17:00</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>（3）The Oxygen 峇里島風夕陽晚餐</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>The Oxygen Beachfront Oasis</t>
         </is>
@@ -2269,124 +2421,121 @@
           <t>芭達雅・帕山</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>包車 / 計程車 (約 15 分鐘)</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>【重點行程】🍑Mo 強烈推薦！首日行程重點，需先透過 KKday/官方粉專預訂席位。</t>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>包車 / 計程車</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>第一天夕陽晚餐，建議先在 KKday 或官方提早訂好位子。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Day 1
-11/25 (週三)</t>
+          <t>11/25 (週三)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>20:30 - 23:00</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>夜生活探索：步行街 / 中天夜市</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>芭達雅步行街 (Walking Street) 或夜市</t>
+          <t>晚間時段</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>（4）晚上夜市或是芭達雅步行街</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>芭達雅夜市 或 Walking Street 步行街 (夜店街)</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>芭達雅海濱路</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+          <t>芭達雅海濱商圈</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>雙條車 / 步行</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>感受芭達雅熱鬧酒吧街或在地夜市小吃；亦可選擇泰式放鬆按摩解疲憊。</t>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>體驗芭達雅在地夜市小吃或熱鬧酒吧夜店街。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>🐘 生態與景觀日：晨間泳池悠閒 ➔ 洗大象餵食半日遊 ➔ 懸崖鳥巢夕陽 ➔ 女王頭高空酒吧</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>🐘 11/26 (週四) 晨間設施 ➔ 洗大象餵食半日遊 ➔ 晚餐咖啡廳 ➔ 夜市/按摩</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Day 2
-11/26 (週四)</t>
+          <t>11/26 (週四)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>08:30 - 11:00</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>早晨悠閒時光：享用早餐 &amp; 泳池設施</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>飯店頂樓無邊際泳池</t>
+          <t>早晨時段</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>（1）早晨休閒時光</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>飯店設施 / 早餐</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>入住飯店內</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>飯店設施</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>度假步調！起得來吃早餐，或在頂樓泳池拍日光大片，享受悠閒晨光。</t>
+          <t>飯店內</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>步行</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>起得來的話可以排早餐，或是直接在飯店享受泳池設施。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Day 2
-11/26 (週四)</t>
+          <t>11/26 (週四)</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>11:30 - 17:00</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>【半日遊】Elephant Jungle 洗大象體驗營</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
+          <t>12:00 - 17:00</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>（2）半日遊：洗與餵食大象</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Elephant Jungle Sanctuary Pattaya</t>
         </is>
@@ -2396,814 +2545,221 @@
           <t>芭達雅近郊</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>營區專車飯店來回接送</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>【重點行程】Jerry &amp; 芊芊🦄 熱推！親手調製草料餵食、泥漿浴、溪水洗澡刷背；自備換洗衣物。</t>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>中午 12 點至下午 5 點，親手調配草料餵食、泥漿浴與溪水洗澡；需備換洗衣物。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Day 2
-11/26 (週四)</t>
+          <t>11/26 (週四)</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>17:30 - 19:30</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>【懸崖夕陽晚餐】極簡風鳥巢海景餐廳</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>The Sky Gallery Pattaya</t>
+          <t>傍晚 17:30</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>（3）景觀咖啡廳或是晚餐</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>The Sky Gallery 鳥巢餐廳 或 ZAMA Skybar</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>芭達雅・皇家懸崖</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>計程車 / 包車 (約 15 分鐘)</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>🍑Mo 推薦極簡鳥巢餐廳！懸崖俯瞰格蘭島夕陽，點泰式料理與熱帶調酒賞落日。</t>
+          <t>帕山 / 中天</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>計程車 / 包車</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>大象行程結束後，可安排景觀咖啡廳放鬆或海景夕陽晚餐。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Day 2
-11/26 (週四)</t>
+          <t>11/26 (週四)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>20:00 - 22:30</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>【夜生活】ZAMA Skybar 女王頭燈光秀</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>ZAMA Skybar Pattaya (38F)</t>
+          <t>晚間時段</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>（3）夜市或泰式按摩</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>芭達雅夜市 或 泰式按摩館</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>中天海灘第一排</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>雙條車 / 計程車</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>芊芊🦄 &amp; 🍑Mo 推薦！38 樓迷幻女王頭燈光藝術秀，拍短影音必訪；或安排泰式精油按摩。</t>
+          <t>市區商圈</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>雙條車 / 步行</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>洗去白天戶外疲勞，享受泰式舒壓按摩或逛夜市。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>🌊 沙灘與海上狂歡日：中天沙灘放鬆 ➔ 藍色懶骨頭下午茶 ➔ 男模郵輪夕陽秀 ➔ 在地花園酒吧</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>🌊 11/27 (週五) 沙灘日（粉紅沙灘、Cave Beach、Dongtan）➔ 晚上夜市或按摩</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Day 3
-11/27 (週五)</t>
+          <t>11/27 (週五)</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>10:00 - 15:30</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>【沙灘日】海風日光浴 &amp; 藍色懶骨頭</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Cave Beach Club / Dongtan Beach</t>
+          <t>日間時段</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>（1）沙灘日放鬆放空</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Cave Beach Club / 粉紅沙灘 (Tutu Beach) / Dongtan Beach</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>中天海灘南區</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+          <t>中天海灘 / 冬潭沙灘</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>包車 / 雙條車</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
-        <is>
-          <t>🍑Mo 推薦 Cave Beach Club（「藍色懶骨頭夕陽墾丁感餐廳 下午去特別美」），享受陽光沙灘。</t>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>享受陽光海風沙灘，可至藍色懶骨頭或粉紅沙灘拍美照喝下午茶。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Day 3
-11/27 (週五)</t>
+          <t>11/27 (週五)</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>16:30 - 20:30</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>【海上狂歡】Ocean Sky 男模郵輪夕陽秀</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Ocean Sky Pattaya (或 Sina Beach Club)</t>
+          <t>傍晚時段</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>（可選）海上夕陽遊艇 / 郵輪</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Ocean Sky 男模郵輪 或 The Garden 168 露天酒吧</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Bali Hai 碼頭外海</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>快艇接駁登船</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>【重點行程】🍑Mo 推薦男模郵輪！夕陽海景、海鮮自助百匯、猛男秀舞互動與釣魷魚，氣氛超嗨。</t>
+          <t>外海碼頭 / 南區</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>快艇接駁 / 計程車</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>傍晚可選擇出海夕陽秀，或造訪在地高 CP 值露天音樂酒吧。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Day 3
-11/27 (週五)</t>
+          <t>11/27 (週五)</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>21:00 - 23:30</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>【在地夜生活】The Garden 168 露天音樂酒吧</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>The Garden 168 Pattaya</t>
+          <t>晚間時段</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>（2）晚上夜市或按摩</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>中天夜市 / 泰式按摩店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>南芭達雅</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>計程車 / 雙條車</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>🍑Mo 推薦當地人高 CP 值露天酒吧，現場 Live 樂團演奏，小酌泰國啤酒聊天放鬆。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>🏙️ 曼谷風華日：包車前往曼谷 ➔ 曼谷飯店入住 ➔ ICONSIAM水上市場 ➔ 璀璨明珠號遊船 ➔ 水母酒吧</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Day 4
-11/28 (週六)</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>10:00 - 12:30</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>芭達雅退房 ➔ 包車前往曼谷市區</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>芭達雅 ➔ 曼谷市區飯店</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>跨城高速公路</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>預約專車包車 (約 2 小時)</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>舒適專車包車直達曼谷飯店，免去拖行李轉車奔波。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Day 4
-11/28 (週六)</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>12:30 - 14:30</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>曼谷飯店辦理入住 &amp; 放行李短歇</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>The Standard Mahanakhon / The Sacha</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>曼谷市區 (沙吞 / 通羅)</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>專車抵達</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>入住設計酒店（The Standard 圓弧大膽設計或 The Sacha 通羅公寓式飯店）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Day 4
-11/28 (週六)</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>15:00 - 18:30</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>【地標旗艦】ICONSIAM 暹羅天地室內水上市場</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>ICONSIAM (SOOKSIAM 室內水上市場)</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>昭披耶河畔</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>BTS 金線 / 接駁船</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>芊芊🦄 推薦「星羅」！室內冷氣水上市場品嚐全泰美食、拍室內瀑布、逛 POP MART 與河畔星巴克。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Day 4
-11/28 (週六)</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>19:00 - 21:30</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>【昭披耶河晚宴】璀璨明珠號豪華遊船</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Wonderful Pearl Cruise (River City 登船)</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>昭披耶河沿線</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>步行 / 接駁船抵碼頭</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>【重點行程】芊芊🦄 熱推浪漫遊船！吹晚風賞鄭王廟大皇宮絕美點燈、享海鮮自助餐與現場爵士樂。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Day 4
-11/28 (週六)</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>22:00 - 00:00</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>【地標高空酒吧】Tichuca 水母發光神樹</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Tichuca Rooftop Bar (T-One 46F)</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>素坤逸通羅區</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>BTS Thong Lo 站步行</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>芊芊🦄 推薦！曼谷最具標誌性阿凡達發光水母吧台，360 度無死角俯瞰曼谷繁華天際線。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>✨ 網美朝聖與星級夜生活：水上馬爾地夫泡泡咖啡廳 ➔ Le Du Kaan 56樓高空晚餐 ➔ 猛男夜店大秀</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>Day 5
-11/29 (週日)</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>10:30 - 14:30</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>【水上馬爾地夫】Bubble in the Forest 咖啡廳</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Bubble in the Forest Cafe</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>佛統府 (曼谷西郊約 45 分鐘)</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>曼谷市區包車一日遊</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>丁 推薦！水上獨立漂浮泡泡涼亭與蒂芬妮藍潟湖，拍照質感絕頂，需提前預訂水上包廂。</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>Day 5
-11/29 (週日)</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>17:00 - 19:30</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>【星級高空晚宴】Le Du Kaan 56 樓泰式饗宴</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Le Du Kaan (The Empire 56F)</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>沙吞金融商圈</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>BTS Chong Nonsi 站步行</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>【重點行程】芊芊🦄 熱情號召「超讚約起來」！米其林名廚 Chef Ton 打造曼谷最高泰式景觀餐廳。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>Day 5
-11/29 (週日)</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>20:30 - 23:30</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>【派對夜生活二選一】男模夜店秀 或 星光沙灘酒吧</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Fake Club Bangkok 或 TRIBE Sky Beach Club</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>匯狂區 / 澎蓬 Emsphere</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>MRT / BTS</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>體驗曼谷傳奇 Fake Club 震撼猛男秀狂歡，或前往 Emsphere 頂樓 TRIBE 星光沙灘泳池酒吧享受微醺。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>🐱 療癒與文青購物日：鱷魚頭水上老街貓貓船 ➔ 阿里文青街區漫步 ➔ 市區手信伴手禮採購</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Day 6
-11/30 (週一)</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>10:00 - 13:30</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>【超療癒體驗】百年水上市場「泰國貓貓船」</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Si Yaek Huatakhe Cafe &amp; Guesthouse</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>拉卡邦區 (百年運河老街)</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>專車包車 / Grab</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>芊芊🦄 推薦泰國貓貓船！乘木造小舟泛舟古運河，與親人店貓親密互動，收益回饋流浪動物保護。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Day 6
-11/30 (週一)</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>14:30 - 17:30</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>【文青漫步】阿里商圈特色探店 &amp; 模擬市民酒吧</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Craftsman Baby Bar / Ari 文青街區</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>拍耶泰阿里區 (BTS Ari)</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>BTS Ari 站步行</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>造訪《模擬市民》風格的 Craftsman Baby Bar 享用下午茶，漫步於曼谷最美綠意文青街區。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>Day 6
-11/30 (週一)</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>18:00 - 21:30</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>伴手禮大採購：Big C Supercenter / 喬德夜市</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Central World 旁 Big C / 喬德夜市</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>曼谷市中心 (BTS Chit Lom)</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>BTS / 步行</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>採購泰國必買手標泰奶、芒果乾、各式零食與泰國藥妝；晚餐品嚐火山排骨與海鮮。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>✈️ 完美收官日：享用悠閒早餐 ➔ 退房打包 ➔ 機場退稅與免稅採購 ➔ 平安返台</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Day 7
-12/01 (週二)</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>09:00 - 11:30</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>悠閒早餐時光 &amp; 飯店辦理退房</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>入住飯店餐廳</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>飯店內</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>步行</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>享用飯店豐盛早餐，整理行李打包伴手禮，11:30 前完成 Check-out。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Day 7
-12/01 (週二)</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>12:00 - 15:00</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>專車接送前往機場 &amp; 退稅通關</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>素萬那普機場 (BKK) / 廊曼機場 (DMK)</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>曼谷國際機場</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>預約專車接送</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>國際航班建議提前 3 小時抵達機場；辦理退稅手續、領取退稅款並於免稅店最後補貨。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Day 7
-12/01 (週二)</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>16:00 - 20:30</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>搭機啟程返台，平安賦歸！</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>國際航班 ➔ 台灣機場</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>曼谷 ➔ 台北/高雄</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>國際航班飛行</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>結束 7 天 6 夜充實精彩的曼谷芭達雅自由行，滿載美好回憶回家！</t>
+          <t>芭達雅市區</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>雙條車 / 步行</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>放鬆享受泰式精油按摩，逛在地夜市品嚐海鮮小吃。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="4">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A3:G3"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3257,7 +2813,7 @@
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>【泰國曼谷】4天3夜自由行懶人包，新手出發前必看！機場交通與景點規劃</t>
         </is>
@@ -3267,7 +2823,7 @@
           <t>2024/09/19</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>▶️ 觀看 YouTube 影片</t>
         </is>
@@ -3277,7 +2833,7 @@
       <c r="A4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>泰國曼谷自由行攻略懶人包 10天9夜行程規劃（曼谷美食、景點、住宿）</t>
         </is>
@@ -3287,7 +2843,7 @@
           <t>2024/05/02</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>▶️ 觀看 YouTube 影片</t>
         </is>
@@ -3297,7 +2853,7 @@
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>曼谷旅遊 在地人的私藏行程！觀光客還不知道的新地方</t>
         </is>
@@ -3307,7 +2863,7 @@
           <t>2025/05/04</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>▶️ 觀看 YouTube 影片</t>
         </is>
@@ -3317,7 +2873,7 @@
       <c r="A6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>曼谷旅遊2026｜平價爽玩全攻略！日式海鮮吃到飽、設計風泳池飯店</t>
         </is>
@@ -3327,7 +2883,7 @@
           <t>2026/05/05</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>▶️ 觀看 YouTube 影片</t>
         </is>
@@ -3337,7 +2893,7 @@
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>2024曼谷自由行｜泰國「免簽」4天3夜全攻略！11景點：鄭王廟拍泰服</t>
         </is>
@@ -3347,7 +2903,7 @@
           <t>2024/09/14</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>▶️ 觀看 YouTube 影片</t>
         </is>
@@ -3357,7 +2913,7 @@
       <c r="A8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>曼谷自由行 七家必吃美食攻略！牛肉湯之王 隱藏無名咖哩蝦</t>
         </is>
@@ -3367,7 +2923,7 @@
           <t>2026/01/02</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>▶️ 觀看 YouTube 影片</t>
         </is>
@@ -3377,7 +2933,7 @@
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>【曼谷自由行2026】 第一次去曼谷必睇！臥佛寺必看位 + 曼谷平價美食</t>
         </is>
@@ -3387,7 +2943,7 @@
           <t>2026/03/06</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>▶️ 觀看 YouTube 影片</t>
         </is>
@@ -3397,7 +2953,7 @@
       <c r="A10" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>【泰國旅遊】曼谷Cloud 11新地標正式開幕！5樓空中花園超大片草地</t>
         </is>
@@ -3407,7 +2963,7 @@
           <t>2026/08/14</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>▶️ 觀看 YouTube 影片</t>
         </is>

--- a/曼谷自由行心願清單.xlsx
+++ b/曼谷自由行心願清單.xlsx
@@ -59,7 +59,7 @@
     <font>
       <name val="微軟正黑體"/>
       <b val="1"/>
-      <color rgb="001B4F72"/>
+      <color rgb="001A5276"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -1234,8 +1234,8 @@
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>行程標記</t>
+          <t>行程安排標記</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>★ 暫定 11/25 (三) 晚餐</t>
+          <t>暫定 11/25 (三) 晚餐</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -1337,9 +1337,9 @@
           <t>10:00 - 22:00 (傍晚 16:30 抵達最佳)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>★ 暫定 11/26 (四) 傍晚候選</t>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1370,9 +1370,9 @@
           <t>11:00 - 23:00 (15:30 - 18:00 最美)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>★ 暫定 11/27 (五) 沙灘日候選</t>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -1403,9 +1403,9 @@
           <t>17:00 - 01:00 (18:30 燈光秀展開)</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>★ 暫定 11/26 (四) 晚間候選</t>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1436,9 +1436,9 @@
           <t>18:00 - 02:00 (21:00 後樂團開唱)</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>★ 暫定 11/27 (五) 晚間候選</t>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>★ 暫定 11/26 (四) 中午半日遊</t>
+          <t>暫定 11/26 (四) 半日遊</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1733,9 +1733,9 @@
           <t>16:00 - 22:00 (登船約 17:00)</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>★ 暫定 11/27 (五) 傍晚候選</t>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1931,9 +1931,9 @@
           <t>入住 15:00 / 退房 12:00</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>★ 暫定 11/25~11/27 住宿候選</t>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1964,9 +1964,9 @@
           <t>入住 15:00 / 退房 12:00</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>★ 暫定 11/25~11/27 住宿候選</t>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -2252,22 +2252,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🗓️ 11/25 - 11/27 芭達雅自由行 暫定計畫行程表</t>
+          <t>🗓️ 芭達雅自由行 暫定計畫行程表 (11/25 - 11/27)</t>
         </is>
       </c>
     </row>
@@ -2279,260 +2277,168 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>時段安排</t>
+          <t>時段 / 順序</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>行程活動項目</t>
+          <t>行程想法 / 項目</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>推薦地點 / 設施</t>
+          <t>實際地點 (未提及則保持空白)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>所在區域</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>交通方式</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>備註提醒</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>🌟 11/25 (週三) 機場前往芭達雅 ➔ 飯店入住 ➔ 峇里島風夕陽晚餐 ➔ 夜市/步行街</t>
+          <t>11/25 週三</t>
         </is>
       </c>
       <c r="B3" s="10" t="n"/>
       <c r="C3" s="10" t="n"/>
       <c r="D3" s="10" t="n"/>
       <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>11/25 (週三)</t>
+          <t>11/25 週三</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>下午時段</t>
+          <t>（1）</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>（1）機場到芭達雅 3 小時</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>曼谷機場 ➔ 芭達雅</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>跨城交通</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>包車直達 (約 2.5~3 小時)</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>建議提前研究並預訂來回包車接送。</t>
+          <t>機場到巴達雅3小時</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr"/>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>第一天去芭達雅包車研究預訂來回</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>11/25 (週三)</t>
+          <t>11/25 週三</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>抵達後</t>
+          <t>（2）</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>（2）先去 Check-in</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>芭達雅預定飯店 (如 Arbour Hotel / Dusit Thani)</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>芭達雅市區</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>專車抵達</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>辦理入住手續放行李梳洗。</t>
-        </is>
-      </c>
+          <t>先去 check in</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>11/25 (週三)</t>
+          <t>11/25 週三</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>傍晚 17:00</t>
+          <t>（3）</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>（3）The Oxygen 峇里島風夕陽晚餐</t>
+          <t>夕陽晚餐峇里島風</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>The Oxygen Beachfront Oasis</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>芭達雅・帕山</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>包車 / 計程車</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>第一天夕陽晚餐，建議先在 KKday 或官方提早訂好位子。</t>
+          <t>The Oxygen Beachfront Oasis เดอะ ออกซิเจน บีชฟรอนท์ โอเอซิส</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>第一天去，先在 KKday 訂好位子</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>11/25 (週三)</t>
+          <t>11/25 週三</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>晚間時段</t>
+          <t>（4）</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>（4）晚上夜市或是芭達雅步行街</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>芭達雅夜市 或 Walking Street 步行街 (夜店街)</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>芭達雅海濱商圈</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>雙條車 / 步行</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>體驗芭達雅在地夜市小吃或熱鬧酒吧夜店街。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
+          <t>晚上夜市或是巴達雅步行街（夜店街）</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="25" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>🐘 11/26 (週四) 晨間設施 ➔ 洗大象餵食半日遊 ➔ 晚餐咖啡廳 ➔ 夜市/按摩</t>
+          <t>11/26 週四</t>
         </is>
       </c>
       <c r="B8" s="10" t="n"/>
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="10" t="n"/>
       <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
-      <c r="G8" s="10" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>11/26 (週四)</t>
+          <t>11/26 週四</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>早晨時段</t>
+          <t>（1）</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>（1）早晨休閒時光</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>飯店設施 / 早餐</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>飯店內</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>步行</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>起得來的話可以排早餐，或是直接在飯店享受泳池設施。</t>
-        </is>
-      </c>
+          <t>早晨（起得來的話可以排早餐或是直接玩飯店設施）</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>11/26 (週四)</t>
+          <t>11/26 週四</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>12:00 - 17:00</t>
+          <t>（2）</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>（2）半日遊：洗與餵食大象</t>
+          <t>半日遊：洗與餵食大象</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2540,226 +2446,109 @@
           <t>Elephant Jungle Sanctuary Pattaya</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>芭達雅近郊</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>營區專車飯店來回接送</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>中午 12 點至下午 5 點，親手調配草料餵食、泥漿浴與溪水洗澡；需備換洗衣物。</t>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>中午 12:00 至下午 17:00</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>11/26 (週四)</t>
+          <t>11/26 週四</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>傍晚 17:30</t>
+          <t>（3）</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>（3）景觀咖啡廳或是晚餐</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>The Sky Gallery 鳥巢餐廳 或 ZAMA Skybar</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>帕山 / 中天</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>計程車 / 包車</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>大象行程結束後，可安排景觀咖啡廳放鬆或海景夕陽晚餐。</t>
-        </is>
-      </c>
+          <t>可排（咖啡廳或是晚餐）</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>11/26 (週四)</t>
+          <t>11/26 週四</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>晚間時段</t>
+          <t>（4）</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>（3）夜市或泰式按摩</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>芭達雅夜市 或 泰式按摩館</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>市區商圈</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>雙條車 / 步行</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>洗去白天戶外疲勞，享受泰式舒壓按摩或逛夜市。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
+          <t>夜市或按摩</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="25" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>🌊 11/27 (週五) 沙灘日（粉紅沙灘、Cave Beach、Dongtan）➔ 晚上夜市或按摩</t>
+          <t>11/27 週五</t>
         </is>
       </c>
       <c r="B13" s="10" t="n"/>
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>11/27 (週五)</t>
+          <t>11/27 週五</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>日間時段</t>
+          <t>（1）</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>（1）沙灘日放鬆放空</t>
+          <t>沙灘日</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Cave Beach Club / 粉紅沙灘 (Tutu Beach) / Dongtan Beach</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>中天海灘 / 冬潭沙灘</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>包車 / 雙條車</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>享受陽光海風沙灘，可至藍色懶骨頭或粉紅沙灘拍美照喝下午茶。</t>
-        </is>
-      </c>
+          <t>例：粉紅沙灘、Dongtan Beach</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>11/27 (週五)</t>
+          <t>11/27 週五</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>傍晚時段</t>
+          <t>（2）</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>（可選）海上夕陽遊艇 / 郵輪</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>Ocean Sky 男模郵輪 或 The Garden 168 露天酒吧</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>外海碼頭 / 南區</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>快艇接駁 / 計程車</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>傍晚可選擇出海夕陽秀，或造訪在地高 CP 值露天音樂酒吧。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>11/27 (週五)</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>晚間時段</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>（2）晚上夜市或按摩</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>中天夜市 / 泰式按摩店</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>芭達雅市區</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>雙條車 / 步行</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>放鬆享受泰式精油按摩，逛在地夜市品嚐海鮮小吃。</t>
-        </is>
-      </c>
+          <t>晚上夜市或按摩</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/曼谷自由行心願清單.xlsx
+++ b/曼谷自由行心願清單.xlsx
@@ -2252,14 +2252,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -2292,6 +2293,11 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>交通方式 (後續填充)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>備註</t>
         </is>
       </c>
@@ -2306,6 +2312,7 @@
       <c r="C3" s="10" t="n"/>
       <c r="D3" s="10" t="n"/>
       <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -2324,7 +2331,8 @@
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr"/>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>第一天去芭達雅包車研究預訂來回</t>
         </is>
@@ -2347,7 +2355,8 @@
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -2370,7 +2379,8 @@
           <t>The Oxygen Beachfront Oasis เดอะ ออกซิเจน บีชฟรอนท์ โอเอซิส</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>第一天去，先在 KKday 訂好位子</t>
         </is>
@@ -2393,7 +2403,8 @@
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="25" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -2405,6 +2416,7 @@
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="10" t="n"/>
       <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -2423,7 +2435,8 @@
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -2446,7 +2459,8 @@
           <t>Elephant Jungle Sanctuary Pattaya</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>中午 12:00 至下午 17:00</t>
         </is>
@@ -2469,7 +2483,8 @@
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -2488,7 +2503,8 @@
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr"/>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr"/>
     </row>
     <row r="13" ht="25" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
@@ -2500,6 +2516,7 @@
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -2522,7 +2539,8 @@
           <t>例：粉紅沙灘、Dongtan Beach</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -2541,14 +2559,15 @@
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/曼谷自由行心願清單.xlsx
+++ b/曼谷自由行心願清單.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="曼谷行程心願清單" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="預定計畫行程" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="影音參考" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="影片提到地點" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +63,38 @@
       <color rgb="001A5276"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <color rgb="002C3E50"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <b val="1"/>
+      <color rgb="00B03A2E"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <b val="1"/>
+      <color rgb="002C3E50"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <b val="1"/>
+      <color rgb="001B4F72"/>
+      <sz val="9.5"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -94,8 +125,14 @@
         <bgColor rgb="00EAEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0047525E"/>
+        <bgColor rgb="0047525E"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -117,11 +154,55 @@
         <color rgb="00D0D3D4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D3D4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D3D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D3D4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D3D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D3D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D3D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D3D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D3D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -156,6 +237,32 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -256,6 +363,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -281,6 +391,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -306,6 +419,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -331,6 +447,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -356,6 +475,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -381,6 +503,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -406,6 +531,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -431,6 +559,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -456,6 +587,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -481,6 +615,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -506,6 +643,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -531,6 +671,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -556,6 +699,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -581,6 +727,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -606,6 +755,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -631,6 +783,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -656,6 +811,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -681,6 +839,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -706,6 +867,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -731,6 +895,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -756,6 +923,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -781,6 +951,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -806,6 +979,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -831,6 +1007,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -856,6 +1035,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -881,6 +1063,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -906,6 +1091,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -931,6 +1119,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2308,11 +2499,11 @@
           <t>11/25 週三</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
+      <c r="B3" s="13" t="n"/>
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="13" t="n"/>
+      <c r="F3" s="14" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -2412,11 +2603,11 @@
           <t>11/26 週四</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="10" t="n"/>
-      <c r="E8" s="10" t="n"/>
-      <c r="F8" s="10" t="n"/>
+      <c r="B8" s="13" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="14" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -2512,11 +2703,11 @@
           <t>11/27 週五</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
+      <c r="B13" s="13" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="14" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -2793,4 +2984,5752 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I116"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>🇹🇭 曼谷自由行 影音參考影片提及地點全攻略 (含米其林指南推薦專區)</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="n"/>
+      <c r="C1" s="10" t="n"/>
+      <c r="D1" s="10" t="n"/>
+      <c r="E1" s="10" t="n"/>
+      <c r="F1" s="10" t="n"/>
+      <c r="G1" s="10" t="n"/>
+      <c r="H1" s="10" t="n"/>
+      <c r="I1" s="10" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>🏆 【精選專區】影音推薦「米其林指南」必吃美食清單（13處必比登推薦與星級入選）</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>序號</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>米其林評級 / 標記</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t>地點名稱（中／英／泰）</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>城市 / 分區 / 鄰近捷運</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>所屬影片</t>
+        </is>
+      </c>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>時間點 (點擊直達)</t>
+        </is>
+      </c>
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t>特色看點 / 招牌餐點</t>
+        </is>
+      </c>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>營業時間 / 建議時段 / 備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>M01</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>🌟 米其林必比登
+(連續多年蟬聯)</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>榮泰豬肉米粉（左店）
+Rung Rueang Pork Noodle</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>澎蓬・Phrom Phong
+(BTS 澎蓬站)</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻
+影片6: 戴妮塔</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>01:13:47 / 03:50</t>
+        </is>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>曼谷傳奇豬肉米粉湯！推薦「酸辣湯米粉」配魚板、手工鮮肉末、脆炸魚皮，湯頭濃郁鮮甜。</t>
+        </is>
+      </c>
+      <c r="I4" s="22" t="inlineStr">
+        <is>
+          <t>08:00–17:00
+天天客滿，建議避開正中午</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>M02</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>🌟 米其林必比登
+(街頭傳奇老店)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Somsak 螃蟹粉絲煲
+Somsak Claypot Crab</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>吞武里・Wongwian Yai
+(BTS 吞武里圓環站)</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>影片6: 戴妮塔</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>炭火砂鍋焗大沙公／巨蝦冬粉煲！冬粉吸飽滿滿黑胡椒香蒜汁與鮮美蟹汁，老饕一致推崇。</t>
+        </is>
+      </c>
+      <c r="I5" s="22" t="inlineStr">
+        <is>
+          <t>15:00–21:30 (週一休)
+人氣排隊名店</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>M03</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>🌟 米其林必比登
+(班塔通熱炒名店)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>艾海鮮
+Aey Seafood (เอ๋ ซีฟู้ด)</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>暹羅・National Stadium
+(BTS 體育館站/班塔通)</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>班塔通美食街平價海鮮天花板！炭烤大頭蝦、香濃黑胡椒草蝦粉絲煲、炒花枝蛤蜊，高CP值。</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t>16:30–23:30
+晚間排隊熱門店</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>M04</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>🌟 米其林必比登
+(30年老字號)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>Elvis Suki 泰式壽喜燒
+Elvis Suki (เอลวิส สุกี้)</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>中山巷・Soi Yotse
+(近 MRT 龍蓮寺站)</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>01:09:27</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>大火快炒乾壽喜燒（Suki Hang），牛肉嫩口、鑊氣十足，沾上濃郁微辣腐乳醬，炭烤扇貝必點。</t>
+        </is>
+      </c>
+      <c r="I7" s="22" t="inlineStr">
+        <is>
+          <t>15:30–23:00
+老饕宵夜名店</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>M05</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>🌟 米其林必比登
+(潮汕老字號魚湯)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>金泡鮮魚粥
+Kimpo Khao Tom Pla</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>班塔通・Banthat Thong
+(BTS 體育館站)</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>01:11:52</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>炭火古法熬煮野生石斑魚片湯泡飯、肥美鮮蚵，湯頭甘醇鮮美無腥味，可加點酥脆炸魚皮。</t>
+        </is>
+      </c>
+      <c r="I8" s="22" t="inlineStr">
+        <is>
+          <t>15:30–22:30
+鮮魚湯泡飯代表</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>M06</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>🌟 米其林必比登
+(泰北依善菜代表)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>沙吞班頌潭青木瓜沙拉
+Baan Somtum Sathorn</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>沙吞・Surasak
+(BTS 蘇拉沙克站)</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>51:00</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>連續多年米其林必比登！超過20種特色青木瓜沙拉（鹹蛋、生蝦、玉米），配泰北脆皮烤雞與炸豬頸肉。</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>11:00–22:00
+環境舒適有空調</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>M07</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>🌟 米其林必比登
+(老城區炭火大鑊)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>安姐脆皮雞肉炒粿條
+Ann Guay Tiew Kua Gai</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>老城區・Phlap Phla Chai
+(MRT 龍蓮寺站)</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>01:04:00</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>炭火大鐵鍋快炒，粿條外脆內軟、鑊氣滿滿，配上嫩雞肉、脆魷魚與半熟流心煎蛋，曼谷第一炒粿條。</t>
+        </is>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>14:00–23:00
+近唐人街</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>M08</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>🌟 米其林必比登
+(唐人街排隊傳奇)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>陳億粿條店
+Nai Ek Roll Noodles</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>唐人街・Chinatown
+(MRT 龍蓮寺站)</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>02:08:00</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>曼谷耀華力路排隊傳奇！招牌「胡椒脆皮燒肉卷粉湯」，白胡椒辛香過癮，脆皮燒肉外脆內多汁。</t>
+        </is>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>08:00–00:00
+唐人街必吃</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>M09</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>🌟 米其林必比登
+(水門市場粉紅店)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>紅大哥水門雞飯
+Go-Ang Pratunam</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>水門・Pratunam
+(BTS 奇隆站)</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻
+影片4: 美食猛男</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>32:00 / 03:54</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>曼谷知名粉紅制服海南雞飯！雞肉滑嫩、雞油飯香氣四溢，附黑蒜甜辣醬與胡椒雞骨清湯。</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t>06:00–22:30
+平價經典</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>🌟 米其林必比登
+(華欣直送海鮮)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>Lay Lao 泰國東北料理
+Lay Lao - Silom</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>席隆・Sala Daeng
+(BTS 莎拉當站/Yada棟)</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>影片7: 喵兔自由行</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>蟬聯多年米其林必比登！華欣直送海鮮，招牌炭烤黑胡椒花枝、酸辣生醃鮮蝦、炸豆腐與泰式炒河粉。</t>
+        </is>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>10:30–21:30
+交通便利、環境乾淨</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>🌟 米其林名廚合作
+(移動景觀餐廳)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>曼谷美食觀光雙層巴士
+Bangkok Thai Bus Tour</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>曼谷老城區巡禮
+(起點：River City 碼頭)</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>影片5: 屠潔</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>00:36</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>全泰首創雙層觀光巴士，環遊大皇宮、鄭王廟等古蹟，車上享用米其林名店 Pad Thai Thip Samai 河粉與咖哩。</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>需事先於官網/Klook預訂
+分午餐/下午茶/晚餐時段</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>✨ 米其林指南入選
+(Lisa 打卡名店)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>萬姐甜品
+Jae Wan (เจ๊วรรณ)</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>班塔通・Banthat Thong
+(BTS 體育館站)</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>Blackpink Lisa 打卡轟動的傳統甜品店！草本黑糖冷熱豆花、鮮奶火山冰、滿滿配料仙草芋圓。</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>13:30–23:30 (週日休)
+宵夜甜點大熱門</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>✨ 米其林指南入選
+(唐人街排隊神攤)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>Guy Kao 炭烤海鮮魷魚
+Guy Kao Grilled Squid</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>唐人街・Chinatown
+(MRT 龍蓮寺站)</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>02:05:00</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>唐人街耀華力路炭火現烤巨型透抽、魷魚卵、魷魚嘴，淋上酸辣帶勁的青檸海鮮辣椒醬。</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>17:45–01:00 (週一休)
+常大排長龍</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>🎬 【完整收錄】8 部 YouTube 攻略影片逐項地點與精確時間軸總覽（美食 / 景點 / 住宿 / 購物）</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>序號</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>米其林評級 / 標記</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>地點名稱（中／英／泰）</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>城市 / 分區 / 鄰近捷運</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>所屬影片</t>
+        </is>
+      </c>
+      <c r="G19" s="17" t="inlineStr">
+        <is>
+          <t>時間點 (點擊直達)</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>特色看點 / 招牌餐點</t>
+        </is>
+      </c>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>營業時間 / 建議時段 / 備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>V1-01</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>住宿</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>素萬那普機場膠囊旅館
+Boxtel @ Suvarnabhumi</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>素萬那普機場 (BKK)
+(機場快線 B 樓層)</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>00:06:30</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>位於素萬那普機場地下 BF 樓層，獨立隔音木質小膠囊房，適合紅眼班機或轉機小憩。</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>24 小時營業
+依小時計費</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t>V1-02</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>沙吞碼頭
+Sathorn Pier (Central Pier)</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>昭披耶河畔
+(BTS Saphan Taksin 站)</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>00:25:00</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>昭披耶河水上交通樞紐，可搭乘藍旗觀光船、橙旗渡輪直達鄭王廟、大皇宮與 ICONSIAM。</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>06:00–19:00
+搭乘交通船主要起點</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>V1-03</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>鄭王廟（黎明寺）
+Wat Arun</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>昭披耶河西岸
+(Tha Tien 碼頭對渡)</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>00:27:10</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>曼谷代表性地標！純白彩瓷馬賽克主塔極其典雅，周邊泰服租借拍照最熱門景點。</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>08:00–18:00
+門票約 200 銖</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>V1-04</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>臥佛寺
+Wat Pho</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>老城區
+(MRT Sanam Chai 站)</t>
+        </is>
+      </c>
+      <c r="F23" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>00:30:55</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>曼谷最古老寺廟！供奉長 46 公尺巨大金身臥佛，佛足鑲嵌 108 尊吉祥螺鈿，泰式按摩發源地。</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>08:00–18:30
+寺內附設正宗按摩院</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>V1-05</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>曼谷大皇宮 &amp; 玉佛寺
+The Grand Palace &amp; Wat Phra Kaew</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>老城區・Sanam Luang
+(MRT Sanam Chai 站)</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>00:34:05</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>泰國暹羅王室宏偉宮殿建築群，金碧輝煌的玉佛寺供奉整塊翡翠雕琢的國寶玉佛像。</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>08:30–15:30
+需著長褲長裙不可露肩</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>V1-06</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>Durian Papa 榴槤甜點
+Durian Papa</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>老城區 / 王郎周邊</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>00:39:05</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>榴槤控必去主題餐廳！專賣金枕頭炭烤榴槤、榴槤霜淇淋、榴槤糯米飯與各式榴槤特調甜品。</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>10:00–19:00
+適合喜愛熱帶水果者</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>V1-07</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>王郎市場（王郎早市）
+Wang Lang Market</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>昭披耶河西岸
+(Wang Lang 碼頭旁)</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>00:41:30</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>泰國在地傳統平民市場！集結平價泰式炸雞、烤豬肉串、傳統椰奶小點、泰式壽司與古早味服飾。</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
+        <is>
+          <t>08:00–17:00
+上午最熱鬧</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>V1-08</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>ICONSIAM 暹羅天地
+ICONSIAM</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>昭披耶河畔
+(金線 Charoen Nakhon 站)</t>
+        </is>
+      </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>00:48:45</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>曼谷指標頂級水岸購物商場，GF 樓層打造全室內冷氣空調「SookSiam 泰國各府特色水上市集」。</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+水岸夜景水舞秀</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>V1-09</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Asiatique 河濱碼頭夜市
+Asiatique The Riverfront</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>昭披耶河畔・Charoenkrung
+(沙吞碼頭有免費接駁船)</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>00:50:50</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>老倉庫改建水岸露天夜市，坐擁巨型摩天輪、旋轉木馬、各國景觀餐廳、伴手禮街與泰拳秀。</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>16:00–00:00
+傍晚搭摩天輪看夕陽極佳</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>V1-10</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>購物</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>Siam Paragon 暹羅百麗宮
+Siam Paragon</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>暹羅商圈・Siam
+(BTS Siam 站直通)</t>
+        </is>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>00:53:27</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>曼谷頂級精品商場天花板，B1 美食街聚集泰國各路排隊美食，地下室擁有暹羅海洋世界。</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+捷運核心大站</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>V1-11</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>購物</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>Siam Center 暹羅中心
+Siam Center</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>暹羅商圈・Siam
+(BTS Siam 站直通)</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>00:55:03</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>主打前衛潮流、泰國本土設計師品牌與熱門快閃公仔展（如夢奇奇 Monchhichi、Care Bears）。</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+年輕文創潮流</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>V1-12</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>購物</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>Siam Discovery 暹羅探索
+Siam Discovery</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>暹羅商圈・Siam
+(BTS Siam 站直通)</t>
+        </is>
+      </c>
+      <c r="F31" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>00:55:31</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>日系簡約風格生活美學選品概念商場，4 樓設有曼谷杜莎夫人蠟像館。</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+日系極簡與潮牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>V1-13</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>購物</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>MBK Center 購物中心
+MBK Center</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>暹羅商圈・National Stadium
+(BTS 國立體育館站直通)</t>
+        </is>
+      </c>
+      <c r="F32" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>00:56:21</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>老字號平價平民百貨，匯集各類泰式伴手禮、手工藝品、3C 配件、平價泰式按摩與特色服飾。</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+買伴手禮好去處</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>V1-14</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>購物</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>Siam Square 暹羅廣場
+Siam Square</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>暹羅商圈・Siam
+(BTS Siam 站)</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
+        <is>
+          <t>00:56:46</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>曼谷年輕流行街區心臟，步行街打卡咖啡館、街頭藝人演出、潮流服飾小店與韓風拍貼機聚集地。</t>
+        </is>
+      </c>
+      <c r="I33" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+週末下午常有街頭活動</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>V1-15</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>JODD FAIRS 喬德夜市
+JODD FAIRS Rama 9</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>拉瑪九・Rama 9
+(MRT Phra Ram 9 站)</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
+        <is>
+          <t>00:59:39</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>曼谷最受觀光客喜愛的都會文青夜市，必吃火山排骨、水果西施冰沙、手抓海鮮、生醃海味。</t>
+        </is>
+      </c>
+      <c r="I34" s="22" t="inlineStr">
+        <is>
+          <t>16:00–00:00
+交通最方便的夜市</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>V1-16</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>席娜卡琳火車鐵道夜市
+Srinagarindra Train Night Market</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>席娜卡琳・Srinagarindra
+(黃線 Suan Luang Rama IX 站)</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
+        <is>
+          <t>01:04:02</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>佔地極廣的復古古董老火車夜市！陳列巨型骨董老爺車、美式復古玩具、各式大型跳蚤市集酒吧。</t>
+        </is>
+      </c>
+      <c r="I35" s="22" t="inlineStr">
+        <is>
+          <t>週四至週日 17:00–01:00
+規模最大最在地</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>V1-17</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>ChaTraMue 手標牌泰茶
+ChaTraMue</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>各大捷運站與商場連鎖</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>01:14:57</t>
+        </is>
+      </c>
+      <c r="H36" s="22" t="inlineStr">
+        <is>
+          <t>泰國國寶級正宗老牌茶葉！必喝手拉泰式奶茶、玫瑰花茶與濃郁泰茶霜淇淋，伴手禮茶罐熱銷。</t>
+        </is>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>依各商場營業時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>V1-18</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>Kub Kao' Kub Pla (吃飯吃魚)
+Kub Kao' Kub Pla</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>各大商場連鎖 (如 ICONSIAM / CentralWorld)</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
+        <is>
+          <t>01:15:52</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>泰國高質感精緻泰式家常菜名店，招牌綠咖哩、冬陰功湯、炸鱸魚與泰味辣炒海鮮，環境優雅。</t>
+        </is>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+適合聚餐家庭用餐</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>V1-19</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>VEGANERIE 純素料理
+VEGANERIE</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>素坤逸・BTS Phrom Phong 周邊</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
+        <is>
+          <t>01:17:12</t>
+        </is>
+      </c>
+      <c r="H38" s="22" t="inlineStr">
+        <is>
+          <t>曼谷最知名的健康純素烘焙蔬食餐廳，主打植物肉漢堡、無蛋奶素食甜點蛋糕與燕麥奶特調。</t>
+        </is>
+      </c>
+      <c r="I38" s="22" t="inlineStr">
+        <is>
+          <t>09:30–21:30
+素食者友善首選</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>V1-20</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>Kanom Siam 泰式斑蘭糕
+Kanom Siam (สยามพารากอน)</t>
+        </is>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>Siam Paragon / 班塔通</t>
+        </is>
+      </c>
+      <c r="F39" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G39" s="21" t="inlineStr">
+        <is>
+          <t>01:18:27</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>現做傳統泰式綠色香蘭葉斑蘭小煎糕，口感Q彈濕潤、充滿椰香與香蘭葉芬芳，排隊點心。</t>
+        </is>
+      </c>
+      <c r="I39" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+銅板價熱門街頭小吃</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>V1-21</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>Nueng Nom Nua 烤吐司鮮奶
+Nueng Nom Nua (หนึ่ง นม นัว)</t>
+        </is>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>班塔通・Banthat Thong
+(BTS 體育館站)</t>
+        </is>
+      </c>
+      <c r="F40" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G40" s="21" t="inlineStr">
+        <is>
+          <t>01:19:37</t>
+        </is>
+      </c>
+      <c r="H40" s="22" t="inlineStr">
+        <is>
+          <t>班塔通天天抽號碼牌的排隊神店！炭烤厚切流心吐司，佐北海道厚鮮奶、泰奶醬、斑蘭醬與生乳。</t>
+        </is>
+      </c>
+      <c r="I40" s="22" t="inlineStr">
+        <is>
+          <t>16:00–01:00
+晚間排隊人潮極多</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>V1-22</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>Kamu Kamu 手搖茶飲
+Kamu Kamu</t>
+        </is>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>各大商場連鎖</t>
+        </is>
+      </c>
+      <c r="F41" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="inlineStr">
+        <is>
+          <t>01:21:27</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>泰國超人氣日系混搭手搖茶，招牌古早味黑糖珍珠恐龍美祿、濃抹茶拿鐵與起司奶蓋茶。</t>
+        </is>
+      </c>
+      <c r="I41" s="22" t="inlineStr">
+        <is>
+          <t>依商場營業時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>V1-23</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>朱拉50廚房
+Chula 50 Kitchen</t>
+        </is>
+      </c>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>班塔通巷內・Chula Soi 50
+(MRT Sam Yan 站)</t>
+        </is>
+      </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G42" s="21" t="inlineStr">
+        <is>
+          <t>01:22:12</t>
+        </is>
+      </c>
+      <c r="H42" s="22" t="inlineStr">
+        <is>
+          <t>曼谷學生與遊客瘋傳的平價神店！招牌「黃金咖哩滑蛋蟹肉飯」大塊蟹肉只要 70-100 銖。</t>
+        </is>
+      </c>
+      <c r="I42" s="22" t="inlineStr">
+        <is>
+          <t>07:00–19:00 (週日休)
+超高 CP 值排隊店</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>V1-24</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>19seafood 平價海鮮熱炒
+19seafood</t>
+        </is>
+      </c>
+      <c r="E43" s="18" t="inlineStr">
+        <is>
+          <t>班塔通・Banthat Thong
+(BTS 體育館站)</t>
+        </is>
+      </c>
+      <c r="F43" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G43" s="21" t="inlineStr">
+        <is>
+          <t>01:24:42</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="inlineStr">
+        <is>
+          <t>班塔通街頭平價泰式海鮮熱炒，各式烤大蝦、酸辣檸檬蒸鱸魚、泰式炒蛤蜊，物美價廉。</t>
+        </is>
+      </c>
+      <c r="I43" s="22" t="inlineStr">
+        <is>
+          <t>16:00–23:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>V1-25</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>MiVana Organic Forest Coffee
+MiVana 森林有機咖啡</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>Srinagarindra
+(近火車夜市)</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G44" s="21" t="inlineStr">
+        <is>
+          <t>01:25:37</t>
+        </is>
+      </c>
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t>隱身在市區的大型自然森林系有機咖啡莊園，四周被高聳綠樹林蔭環繞，環境極度放鬆。</t>
+        </is>
+      </c>
+      <c r="I44" s="22" t="inlineStr">
+        <is>
+          <t>07:30–17:30
+極美綠意採光</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>V1-26</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>Grandma's Garden.BKK 露營咖啡
+Grandma's Garden</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>近郊綠意庭園</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G45" s="21" t="inlineStr">
+        <is>
+          <t>01:27:52</t>
+        </is>
+      </c>
+      <c r="H45" s="22" t="inlineStr">
+        <is>
+          <t>戶外露營風花園草坪咖啡廳，提供野餐椅、露營帳篷造景，寵物友善空間。</t>
+        </is>
+      </c>
+      <c r="I45" s="22" t="inlineStr">
+        <is>
+          <t>10:00–19:00 (週二休)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>V1-27</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>Ittha Boutique Cafe 古堡咖啡
+Ittha Boutique Cafe</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>素坤逸・Punnawithi 巷內</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G46" s="21" t="inlineStr">
+        <is>
+          <t>01:30:07</t>
+        </is>
+      </c>
+      <c r="H46" s="22" t="inlineStr">
+        <is>
+          <t>高聳羅馬拱門、旋轉階梯與斑駁紅磚古堡風格精品咖啡廳，宛如走入歐洲中世紀莊園。</t>
+        </is>
+      </c>
+      <c r="I46" s="22" t="inlineStr">
+        <is>
+          <t>08:00–17:00
+攝影愛好者必訪</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
+        <is>
+          <t>V1-28</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>Ground Coffee 復古紅磚咖啡
+Ground Coffee</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>沙吞・Sathorn 巷弄</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G47" s="21" t="inlineStr">
+        <is>
+          <t>01:32:17</t>
+        </is>
+      </c>
+      <c r="H47" s="22" t="inlineStr">
+        <is>
+          <t>隱身住宅巷弄的安靜紅磚手沖咖啡廳，自然採光天窗，提供頂級單品手沖咖啡與現烤司康。</t>
+        </is>
+      </c>
+      <c r="I47" s="22" t="inlineStr">
+        <is>
+          <t>08:00–17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>V1-29</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>住宿</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>Siam Eco Hostel
+暹羅生態青年旅館</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>暹羅・Ratchathewi
+(BTS 拉差貼威站 1分鐘)</t>
+        </is>
+      </c>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G48" s="21" t="inlineStr">
+        <is>
+          <t>01:35:42</t>
+        </is>
+      </c>
+      <c r="H48" s="22" t="inlineStr">
+        <is>
+          <t>離捷運站超近、步行可達 Siam 商圈，實木溫馨設計風格，單人床位與雙人房型齊全，乾淨高CP值。</t>
+        </is>
+      </c>
+      <c r="I48" s="22" t="inlineStr">
+        <is>
+          <t>交通位置極佳</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>V1-30</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>住宿</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>Hostel Urby 河景青旅
+Hostel Urby</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>昭披耶河畔・Talat Noi
+(近 MRT Wat Mangkon)</t>
+        </is>
+      </c>
+      <c r="F49" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G49" s="21" t="inlineStr">
+        <is>
+          <t>01:40:02</t>
+        </is>
+      </c>
+      <c r="H49" s="22" t="inlineStr">
+        <is>
+          <t>坐落昭披耶河水岸第一排！附設河畔露天景觀咖啡吧與酒吧，夕陽西下時湄南河景色無敵。</t>
+        </is>
+      </c>
+      <c r="I49" s="22" t="inlineStr">
+        <is>
+          <t>老城區水岸景觀</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>V1-31</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>住宿</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>Warm Window Silom 青旅
+Warm Window Silom</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>席隆・Silom
+(BTS 蘇拉沙克站 8分鐘)</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G50" s="21" t="inlineStr">
+        <is>
+          <t>01:43:52</t>
+        </is>
+      </c>
+      <c r="H50" s="22" t="inlineStr">
+        <is>
+          <t>席隆商業區寧靜巷弄內的溫馨木質青旅，公共廚房與交誼空間舒服，周邊生活機能極佳。</t>
+        </is>
+      </c>
+      <c r="I50" s="22" t="inlineStr">
+        <is>
+          <t>氛圍最溫馨</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="18" t="inlineStr">
+        <is>
+          <t>V1-32</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>住宿</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>Tiang Studio 田舍工業風青旅
+Tiang Studio</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="inlineStr">
+        <is>
+          <t>席隆 / 沙吞周邊</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G51" s="21" t="inlineStr">
+        <is>
+          <t>01:49:12</t>
+        </is>
+      </c>
+      <c r="H51" s="22" t="inlineStr">
+        <is>
+          <t>俐落黑灰金屬工業風網美青旅，採光天井與現代藝術陳設，年輕旅人極度喜愛。</t>
+        </is>
+      </c>
+      <c r="I51" s="22" t="inlineStr">
+        <is>
+          <t>工業風設計感</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>V1-33</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>住宿</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>Tamni 曼谷青旅天花板
+Tamni Design Hostel</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>華藍蓬・Hua Lamphong
+(MRT 華藍蓬站 5分鐘)</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>影片1: 創世小夫妻</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="inlineStr">
+        <is>
+          <t>01:52:51</t>
+        </is>
+      </c>
+      <c r="H52" s="22" t="inlineStr">
+        <is>
+          <t>被譽為曼谷青年旅館天花板！大片清水模、日式禪風庭園、自然綠植與質感水療設施。</t>
+        </is>
+      </c>
+      <c r="I52" s="22" t="inlineStr">
+        <is>
+          <t>頂級設計旅宿</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>V2-01</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>住宿</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>Holiday Inn Express Bangkok Siam
+曼谷暹羅假日快捷酒店</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="inlineStr">
+        <is>
+          <t>暹羅・National Stadium
+(BTS 體育館站 2分鐘)</t>
+        </is>
+      </c>
+      <c r="F53" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G53" s="21" t="inlineStr">
+        <is>
+          <t>Day 1~7</t>
+        </is>
+      </c>
+      <c r="H53" s="22" t="inlineStr">
+        <is>
+          <t>對面即為 MBK，步行直達 Siam Paragon，地理位置無懈可擊，附免費豐富早餐與乾淨舒適房型。</t>
+        </is>
+      </c>
+      <c r="I53" s="22" t="inlineStr">
+        <is>
+          <t>交通與生活機能極優</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>V2-02</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>HAAB 班塔通炭火雞蛋糕
+HAAB</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>班塔通・Banthat Thong
+(BTS 體育館站)</t>
+        </is>
+      </c>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H54" s="22" t="inlineStr">
+        <is>
+          <t>班塔通人氣爆表街頭小吃！古法炭火熱烤雞蛋糕，外層微酥、內餡有爆漿鹹蛋黃奶油流沙。</t>
+        </is>
+      </c>
+      <c r="I54" s="22" t="inlineStr">
+        <is>
+          <t>15:00–00:00
+熱門街頭小吃</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>V2-03</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
+          <t>Shall We Meet And Eat
+Shall We Meet And Eat &amp; ZABB</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>班塔通・Banthat Thong
+(BTS 體育館站)</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G55" s="21" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="H55" s="22" t="inlineStr">
+        <is>
+          <t>班塔通街邊微醺酒吧與泰式酸辣熱炒小館，適合逛街後點幾盤涼拌海鮮小酌放鬆。</t>
+        </is>
+      </c>
+      <c r="I55" s="22" t="inlineStr">
+        <is>
+          <t>17:00–01:00
+宵夜微醺好選擇</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>V2-04</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>恰圖恰週末市集
+Chatuchak Weekend Market</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="inlineStr">
+        <is>
+          <t>恰圖恰・Mo Chit
+(BTS Mo Chit / MRT Kamphaeng Phet)</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G56" s="21" t="inlineStr">
+        <is>
+          <t>Day 2</t>
+        </is>
+      </c>
+      <c r="H56" s="22" t="inlineStr">
+        <is>
+          <t>全世界最大週末露天跳蚤市集！超過 15,000 個攤位，手作服飾、香氛精油、家飾品與街頭美食。</t>
+        </is>
+      </c>
+      <c r="I56" s="22" t="inlineStr">
+        <is>
+          <t>週六、週日 09:00–18:00
+必逛市集</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>V2-05</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>Let's Relax 連鎖泰式按摩
+Let's Relax Spa</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>全曼谷各大據點 (Siam / MBK 等)</t>
+        </is>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G57" s="21" t="inlineStr">
+        <is>
+          <t>Day 2</t>
+        </is>
+      </c>
+      <c r="H57" s="22" t="inlineStr">
+        <is>
+          <t>泰國知名高品質平價連鎖按摩品牌，芳香精油按摩、泰式古法草藥球熱敷，結束提供芒果糯米飯。</t>
+        </is>
+      </c>
+      <c r="I57" s="22" t="inlineStr">
+        <is>
+          <t>10:00–00:00
+建議先在平台買券預訂</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>V2-06</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>After You Dessert Cafe 雪花冰
+After You Dessert Cafe</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>各大商場 (如 CentralWorld / Siam Paragon)</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G58" s="21" t="inlineStr">
+        <is>
+          <t>35:30</t>
+        </is>
+      </c>
+      <c r="H58" s="22" t="inlineStr">
+        <is>
+          <t>泰國甜點霸主！招牌泰式奶茶雪花冰、芒果糯米刨冰、蜜糖吐司，冰心內藏糯米仙草驚喜。</t>
+        </is>
+      </c>
+      <c r="I58" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+逛街必吃甜品</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>V2-07</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>購物</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>Central World 中央世界商場
+Central World</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="inlineStr">
+        <is>
+          <t>奇隆・Chit Lom
+(BTS Chit Lom 站天橋直通)</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G59" s="21" t="inlineStr">
+        <is>
+          <t>Day 2</t>
+        </is>
+      </c>
+      <c r="H59" s="22" t="inlineStr">
+        <is>
+          <t>曼谷市中心最大巨型商場，匯集各式品牌旗艦店、美食街與泰國最大的 Big C Supercenter 對面。</t>
+        </is>
+      </c>
+      <c r="I59" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+跨年與節慶核心</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>V2-08</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>Factory Coffee Bangkok
+曼谷冠軍精品咖啡</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="inlineStr">
+        <is>
+          <t>披耶泰・Phaya Thai
+(BTS/機場快線 Phaya Thai 站旁)</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G60" s="21" t="inlineStr">
+        <is>
+          <t>41:30</t>
+        </is>
+      </c>
+      <c r="H60" s="22" t="inlineStr">
+        <is>
+          <t>泰國世界咖啡師大賽冠軍名店！招牌特調 Supreme、Phayathai，桌邊現場搖製注咖啡極具儀式感。</t>
+        </is>
+      </c>
+      <c r="I60" s="22" t="inlineStr">
+        <is>
+          <t>08:00–16:30
+精品咖啡必訪名店</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>V2-09</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>愛侶灣四面佛
+Erawan Shrine</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>奇隆・Chit Lom
+(BTS Chit Lom 站旁)</t>
+        </is>
+      </c>
+      <c r="F61" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G61" s="21" t="inlineStr">
+        <is>
+          <t>Day 3</t>
+        </is>
+      </c>
+      <c r="H61" s="22" t="inlineStr">
+        <is>
+          <t>曼谷市中心香火最鼎盛的梵天四面佛神壇，傳說有求必應，信徒還願常請泰國傳統舞者獻舞。</t>
+        </is>
+      </c>
+      <c r="I61" s="22" t="inlineStr">
+        <is>
+          <t>06:00–22:00
+心誠則靈必拜</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>V2-10</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>購物</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>Gentle Woman 旗艦店
+Gentle Woman Siam Square</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="inlineStr">
+        <is>
+          <t>暹羅廣場・Siam Square</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G62" s="21" t="inlineStr">
+        <is>
+          <t>Day 3</t>
+        </is>
+      </c>
+      <c r="H62" s="22" t="inlineStr">
+        <is>
+          <t>泰國席捲全亞洲的流行女裝潮牌！帆布字母托特包、時尚潮流服飾，4層樓旗艦店超好買。</t>
+        </is>
+      </c>
+      <c r="I62" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+泰國必買伴手禮包包</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>V2-11</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>購物</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>Daddy And The Muscle Academy
+Daddy &amp; Muscle Academy</t>
+        </is>
+      </c>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>暹羅廣場・Siam Square</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G63" s="21" t="inlineStr">
+        <is>
+          <t>Day 3</t>
+        </is>
+      </c>
+      <c r="H63" s="22" t="inlineStr">
+        <is>
+          <t>夢幻美式復古少女雜貨選物店，粉彩服飾、文具貼紙、可愛飾品與韓式四格拍貼機。</t>
+        </is>
+      </c>
+      <c r="I63" s="22" t="inlineStr">
+        <is>
+          <t>11:30–20:30
+少女心爆棚</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>V2-12</t>
+        </is>
+      </c>
+      <c r="B64" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr">
+        <is>
+          <t>Inter Restaurants since 1981
+Inter Restaurant</t>
+        </is>
+      </c>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>暹羅廣場・Siam Square</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G64" s="21" t="inlineStr">
+        <is>
+          <t>48:00</t>
+        </is>
+      </c>
+      <c r="H64" s="22" t="inlineStr">
+        <is>
+          <t>暹羅廣場經營超過 40 年的超平價泰國家常菜老店！炒泰式媽媽麵、綠咖哩雞、泰式蛋包飯，便宜好吃。</t>
+        </is>
+      </c>
+      <c r="I64" s="22" t="inlineStr">
+        <is>
+          <t>11:00–20:15
+暹羅商圈高CP值午餐</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>V2-13</t>
+        </is>
+      </c>
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D65" s="20" t="inlineStr">
+        <is>
+          <t>王權 Mahanakhon SkyWalk 觀景台
+King Power Mahanakhon</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>沖暖詩・Chong Nonsi
+(BTS Chong Nonsi 站直通)</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G65" s="21" t="inlineStr">
+        <is>
+          <t>Day 3</t>
+        </is>
+      </c>
+      <c r="H65" s="22" t="inlineStr">
+        <is>
+          <t>全泰國最高 78 樓頂層！踏上全透明懸空高空玻璃平台，俯瞰曼谷百萬璀璨日落與夜景。</t>
+        </is>
+      </c>
+      <c r="I65" s="22" t="inlineStr">
+        <is>
+          <t>10:00–19:00
+夕陽黃金時段最熱門</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>V2-14</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D66" s="20" t="inlineStr">
+        <is>
+          <t>安樂園 80年老牌港泰早餐
+On Lok Yun (ออน ล็อก หยุ่น)</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>老城區・Charoen Krung
+(MRT Sam Yot 站 2分鐘)</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G66" s="21" t="inlineStr">
+        <is>
+          <t>56:30</t>
+        </is>
+      </c>
+      <c r="H66" s="22" t="inlineStr">
+        <is>
+          <t>開業超過 80 年的懷舊古早味洋食早餐冰室！必吃咖椰醬烤吐司、蒸麵包、半熟雙蛋佐培根熱狗與美祿。</t>
+        </is>
+      </c>
+      <c r="I66" s="22" t="inlineStr">
+        <is>
+          <t>06:00–14:30
+排隊經典古早味</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>V2-15</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D67" s="20" t="inlineStr">
+        <is>
+          <t>One More Thai 泰式按摩
+One More Thai Massage</t>
+        </is>
+      </c>
+      <c r="E67" s="18" t="inlineStr">
+        <is>
+          <t>奇隆・Chit Lom
+(BTS Chit Lom 站 1分鐘)</t>
+        </is>
+      </c>
+      <c r="F67" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G67" s="21" t="inlineStr">
+        <is>
+          <t>Day 4</t>
+        </is>
+      </c>
+      <c r="H67" s="22" t="inlineStr">
+        <is>
+          <t>奇隆站旁交通極便的平價優質按摩館，泰式草本足部按摩、古法全身拉筋指壓，平價乾淨。</t>
+        </is>
+      </c>
+      <c r="I67" s="22" t="inlineStr">
+        <is>
+          <t>10:00–23:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="32" customHeight="1">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>V2-16</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" s="20" t="inlineStr">
+        <is>
+          <t>The One Ratchada 拉差達火車夜市
+The One Ratchada</t>
+        </is>
+      </c>
+      <c r="E68" s="18" t="inlineStr">
+        <is>
+          <t>文化中心・Thailand Cultural Centre
+(MRT 泰國文化中心站)</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G68" s="21" t="inlineStr">
+        <is>
+          <t>Day 4</t>
+        </is>
+      </c>
+      <c r="H68" s="22" t="inlineStr">
+        <is>
+          <t>原拉差達火車夜市原址重開！純白色文青帳篷排列，走道寬敞乾淨，聚集各式特色泰味小吃與露天酒吧。</t>
+        </is>
+      </c>
+      <c r="I68" s="22" t="inlineStr">
+        <is>
+          <t>17:00–00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>V2-17</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D69" s="20" t="inlineStr">
+        <is>
+          <t>Bubble in the Forest Café
+水上馬爾地夫咖啡廳</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>佛統府・Phutthamonthon
+(曼谷市區出發車程約40分鐘)</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻
+影片5: 屠潔</t>
+        </is>
+      </c>
+      <c r="G69" s="21" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="H69" s="22" t="inlineStr">
+        <is>
+          <t>風靡全網的「曼谷近郊小馬爾地夫」！水藍色潟湖環繞圓形木棧道涼亭，拍照極度夢幻，需先預約。</t>
+        </is>
+      </c>
+      <c r="I69" s="22" t="inlineStr">
+        <is>
+          <t>10:00–21:00
+強烈建議包車前往</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="32" customHeight="1">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>V2-18</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>購物</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>Terminal 21 Rama 3 航廈商場
+Terminal 21 Rama 3</t>
+        </is>
+      </c>
+      <c r="E70" s="18" t="inlineStr">
+        <is>
+          <t>拉瑪三・Rama 3
+(BRT Charoenrat 站 / 昭披耶河畔)</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G70" s="21" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="H70" s="22" t="inlineStr">
+        <is>
+          <t>曼谷最新航廈主題百貨！每層樓以日本、英國、法國、加勒比海等各國風情打造，平價美食街 Pier 21 極便宜。</t>
+        </is>
+      </c>
+      <c r="I70" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>V2-19</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D71" s="20" t="inlineStr">
+        <is>
+          <t>水門寺巨型金色大佛
+Wat Paknam Phasi Charoen</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>吞武里・Phasi Charoen
+(MRT Bang Phai 站)</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G71" s="21" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="H71" s="22" t="inlineStr">
+        <is>
+          <t>曼谷近期最震撼新地標！高達 69 公尺（約20層樓）的巨型純金坐佛，白塔頂樓藏有魔幻翠綠琉璃佛塔。</t>
+        </is>
+      </c>
+      <c r="I71" s="22" t="inlineStr">
+        <is>
+          <t>08:00–18:00
+可搭長尾船從河上仰望</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>V2-20</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>邢泰記 傳統近百年古法咖啡
+Kope Hya Tai Kee</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="inlineStr">
+        <is>
+          <t>老城區・Phra Nakhon
+(大鞦韆 Giant Swing 旁)</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G72" s="21" t="inlineStr">
+        <is>
+          <t>01:13:20</t>
+        </is>
+      </c>
+      <c r="H72" s="22" t="inlineStr">
+        <is>
+          <t>近百年歷史傳統咖啡早餐老店，招牌鐵鍋煎蛋（Kai Kata）、古法黑咖啡、蒸吐司沾綠咖椰醬。</t>
+        </is>
+      </c>
+      <c r="I72" s="22" t="inlineStr">
+        <is>
+          <t>07:00–20:00
+老曼谷在地風情</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>V2-21</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>Sense Of Thai 傳統泰服租借
+Sense Of Thai</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>老城區・Tha Maharaj 碼頭商場 2F</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G73" s="21" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="H73" s="22" t="inlineStr">
+        <is>
+          <t>曼谷質感公認最高級傳統泰服店！色系高級典雅，布料精緻，含專人妝髮與配件，直通碼頭搭船拍鄭王廟。</t>
+        </is>
+      </c>
+      <c r="I73" s="22" t="inlineStr">
+        <is>
+          <t>09:30–18:30
+熱門建議先預約</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="32" customHeight="1">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>V2-22</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <t>昭披耶河公主號遊輪晚宴
+Chao Phraya Princess Cruise</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>昭披耶河
+(ICONSIAM / Asiatique 登船)</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G74" s="21" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="H74" s="22" t="inlineStr">
+        <is>
+          <t>經典湄南河夜遊郵輪！2小時航程享用豐富海鮮牛排自助晚餐、現場樂隊 LIVE 演奏，飽覽鄭王廟夜間燈光秀。</t>
+        </is>
+      </c>
+      <c r="I74" s="22" t="inlineStr">
+        <is>
+          <t>約 19:30 出航 (需預約)
+氣氛極佳</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>V2-23</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" s="20" t="inlineStr">
+        <is>
+          <t>丹嫩莎朵水上市場
+Damnoen Saduak Floating Market</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>叻丕府・Ratchaburi
+(曼谷市區車程約 1.5 小時)</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G75" s="21" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="H75" s="22" t="inlineStr">
+        <is>
+          <t>泰國最具代表性古老水上市場！搭手搖舢舨船穿梭河道，與兩側水上船家購買米粉湯、烤香蕉與芒果糯米。</t>
+        </is>
+      </c>
+      <c r="I75" s="22" t="inlineStr">
+        <is>
+          <t>07:00–17:00
+通常安排清晨出發一日遊</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>V2-24</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>美功鐵道市場
+Maeklong Railway Market</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>夜功府・Samut Songkhram
+(曼谷車程約 1.5 小時)</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G76" s="21" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="H76" s="22" t="inlineStr">
+        <is>
+          <t>世界奇觀！傳統菜市場就蓋在鐵軌上，火車鳴笛緩緩駛入時，攤販以秒速收起遮陽棚與攤位，擦身而過。</t>
+        </is>
+      </c>
+      <c r="I76" s="22" t="inlineStr">
+        <is>
+          <t>每日配合火車班次收棚
+約 08:30, 11:10, 14:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="18" t="inlineStr">
+        <is>
+          <t>V2-25</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D77" s="20" t="inlineStr">
+        <is>
+          <t>安帕瓦水上市場
+Amphawa Floating Market</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>夜功府・Samut Songkhram</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G77" s="21" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="H77" s="22" t="inlineStr">
+        <is>
+          <t>泰國在地人最愛的黃昏水上市場！兩岸木造老屋林立，品嚐現烤海鮮大頭蝦，夜間可搭船深入紅樹林賞螢火蟲。</t>
+        </is>
+      </c>
+      <c r="I77" s="22" t="inlineStr">
+        <is>
+          <t>週五至週日 14:00–21:00
+螢火蟲遊船約 60 銖</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>V2-26</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>MEENA Café 稻田景觀咖啡
+MEENA Café</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>北碧府・Kanchanaburi</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G78" s="21" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="H78" s="22" t="inlineStr">
+        <is>
+          <t>北碧府爆紅網美咖啡！延伸在綠油油稻田中央的木棧道與涼亭，背靠壯麗山景遠眺宏偉「虎穴寺」。</t>
+        </is>
+      </c>
+      <c r="I78" s="22" t="inlineStr">
+        <is>
+          <t>08:30–18:30
+北碧必訪美拍點</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="18" t="inlineStr">
+        <is>
+          <t>V2-27</t>
+        </is>
+      </c>
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D79" s="20" t="inlineStr">
+        <is>
+          <t>桂河大橋
+River Kwai Bridge</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr">
+        <is>
+          <t>北碧府・Kanchanaburi</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G79" s="21" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="H79" s="22" t="inlineStr">
+        <is>
+          <t>二戰著名歷史遺跡「死亡鐵路」代表建築，跨越桂河的鐵橋仍有火車行駛，可漫步鐵軌拍照。</t>
+        </is>
+      </c>
+      <c r="I79" s="22" t="inlineStr">
+        <is>
+          <t>全天開放
+二戰歷史地標</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>V2-28</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>Tham Krasae 死亡鐵路木棧道
+Tham Krasae &amp; Krasae Cave</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="inlineStr">
+        <is>
+          <t>北碧府・Kanchanaburi</t>
+        </is>
+      </c>
+      <c r="F80" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G80" s="21" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="H80" s="22" t="inlineStr">
+        <is>
+          <t>死亡鐵路最險峻精華段！懸崖峭壁旁緊貼桂河搭建的百年高架木製鐵軌，旁有安置佛像的天然石灰岩洞穴。</t>
+        </is>
+      </c>
+      <c r="I80" s="22" t="inlineStr">
+        <is>
+          <t>全天開放
+拍照需注意腳下安全</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>V2-29</t>
+        </is>
+      </c>
+      <c r="B81" s="18" t="inlineStr">
+        <is>
+          <t>住宿</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>The FloatHouse River Kwai Resort
+桂河水上浮屋生態度假村</t>
+        </is>
+      </c>
+      <c r="E81" s="18" t="inlineStr">
+        <is>
+          <t>北碧府・桂河水畔
+(需搭船抵達度假村)</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G81" s="21" t="inlineStr">
+        <is>
+          <t>Day 8</t>
+        </is>
+      </c>
+      <c r="H81" s="22" t="inlineStr">
+        <is>
+          <t>全木質打造頂級漂浮水上別墅！每間房皆有專屬私人生態河景露台，躺在吊床上聽桂河潺潺流水，宛如世外桃源。</t>
+        </is>
+      </c>
+      <c r="I81" s="22" t="inlineStr">
+        <is>
+          <t>北碧府頂級度假體驗</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>V2-30</t>
+        </is>
+      </c>
+      <c r="B82" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>北碧府野生動物園
+Safari Park Kanchanaburi</t>
+        </is>
+      </c>
+      <c r="E82" s="18" t="inlineStr">
+        <is>
+          <t>北碧府・Bo Phloi</t>
+        </is>
+      </c>
+      <c r="F82" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G82" s="21" t="inlineStr">
+        <is>
+          <t>Day 9</t>
+        </is>
+      </c>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t>超火紅打卡景點！搭乘敞篷專屬吉普車開入長頸鹿園區，長頸鹿探入車內互動、零距離合照餵食。</t>
+        </is>
+      </c>
+      <c r="I82" s="22" t="inlineStr">
+        <is>
+          <t>09:00–17:00
+吉普車長頸鹿拍照需提前預約</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="18" t="inlineStr">
+        <is>
+          <t>V2-31</t>
+        </is>
+      </c>
+      <c r="B83" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D83" s="20" t="inlineStr">
+        <is>
+          <t>The Village Farm To Café
+北碧莊園咖啡</t>
+        </is>
+      </c>
+      <c r="E83" s="18" t="inlineStr">
+        <is>
+          <t>北碧府・Kanchanaburi</t>
+        </is>
+      </c>
+      <c r="F83" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G83" s="21" t="inlineStr">
+        <is>
+          <t>Day 9</t>
+        </is>
+      </c>
+      <c r="H83" s="22" t="inlineStr">
+        <is>
+          <t>巨型黑色歐式穀倉莊園咖啡廳，後方有大片向日葵花海、草坪與落羽松，招牌烏龜哈密瓜吐司與各式特調料理。</t>
+        </is>
+      </c>
+      <c r="I83" s="22" t="inlineStr">
+        <is>
+          <t>09:00–21:00
+莊園環境優美</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>V2-32</t>
+        </is>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>虎穴寺
+Wat Tham Suea</t>
+        </is>
+      </c>
+      <c r="E84" s="18" t="inlineStr">
+        <is>
+          <t>北碧府・Tha Muang</t>
+        </is>
+      </c>
+      <c r="F84" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G84" s="21" t="inlineStr">
+        <is>
+          <t>Day 9</t>
+        </is>
+      </c>
+      <c r="H84" s="22" t="inlineStr">
+        <is>
+          <t>雄踞山頂的壯觀佛寺！供奉 18 公尺高巨型金色佛像與九層中式寶塔，登頂眺望 360 度遼闊稻田平原美景。</t>
+        </is>
+      </c>
+      <c r="I84" s="22" t="inlineStr">
+        <is>
+          <t>08:00–17:00
+有纜車可搭上山</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>V2-33</t>
+        </is>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>住宿</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D85" s="20" t="inlineStr">
+        <is>
+          <t>ASAI Bangkok Chinatown
+曼谷唐人街雅詩閣潮流酒店</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>唐人街・Chinatown
+(MRT 龍蓮寺站 2分鐘)</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G85" s="21" t="inlineStr">
+        <is>
+          <t>Day 9~10</t>
+        </is>
+      </c>
+      <c r="H85" s="22" t="inlineStr">
+        <is>
+          <t>座落於曼谷耀華力路心臟！新潮現代生活風格旅店，下樓就是熱鬧非凡的唐人街小吃夜市，隔音極佳。</t>
+        </is>
+      </c>
+      <c r="I85" s="22" t="inlineStr">
+        <is>
+          <t>吃唐人街美食首選</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>V2-34</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D86" s="20" t="inlineStr">
+        <is>
+          <t>耀華力古早味爆漿炭烤麵包
+Yaowarat Toasted Bread</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="inlineStr">
+        <is>
+          <t>唐人街・Chinatown
+(MRT 龍蓮寺站)</t>
+        </is>
+      </c>
+      <c r="F86" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G86" s="21" t="inlineStr">
+        <is>
+          <t>02:07:30</t>
+        </is>
+      </c>
+      <c r="H86" s="22" t="inlineStr">
+        <is>
+          <t>唐人街傳奇排隊點心！小餐包在炭火上烤到外皮酥脆，剪開灌入滿滿香蘭葉咖椰、濃巧克力或奶油流沙餡。</t>
+        </is>
+      </c>
+      <c r="I86" s="22" t="inlineStr">
+        <is>
+          <t>17:00–00:00 (週一休)
+人手一袋熱門排隊美食</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>V2-35</t>
+        </is>
+      </c>
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>南豆腐
+Nam Tao Hu (น้ำเต้าหู้)</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
+          <t>唐人街・Chinatown
+(MRT 龍蓮寺站)</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G87" s="21" t="inlineStr">
+        <is>
+          <t>02:11:30</t>
+        </is>
+      </c>
+      <c r="H87" s="22" t="inlineStr">
+        <is>
+          <t>耀華力路懷舊甜品老字號！傳統炭香手工豆漿、熱豆花加脆油條，草本甘甜消夜點心。</t>
+        </is>
+      </c>
+      <c r="I87" s="22" t="inlineStr">
+        <is>
+          <t>08:00–22:00
+古早味甜品</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>V2-36</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D88" s="20" t="inlineStr">
+        <is>
+          <t>龍頭咖啡 耀華力店
+Lhong Tou Cafe</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>唐人街・Chinatown
+(MRT 龍蓮寺站)</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G88" s="21" t="inlineStr">
+        <is>
+          <t>02:13:00</t>
+        </is>
+      </c>
+      <c r="H88" s="22" t="inlineStr">
+        <is>
+          <t>新潮中式蒸籠早茶咖啡廳！立體雙層高架鐵梯座位設計，招牌九宮格精緻清粥小菜組、黃金流沙包與花茶。</t>
+        </is>
+      </c>
+      <c r="I88" s="22" t="inlineStr">
+        <is>
+          <t>08:00–22:00
+拍照打卡熱門店</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="32" customHeight="1">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>V2-37</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>購物</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D89" s="20" t="inlineStr">
+        <is>
+          <t>Siam Premium Outlets Bangkok
+暹羅名品奧特萊斯</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="inlineStr">
+        <is>
+          <t>素萬那普機場東側
+(機場車程約 15 分鐘)</t>
+        </is>
+      </c>
+      <c r="F89" s="18" t="inlineStr">
+        <is>
+          <t>影片2: 2A夫妻</t>
+        </is>
+      </c>
+      <c r="G89" s="21" t="inlineStr">
+        <is>
+          <t>Day 10</t>
+        </is>
+      </c>
+      <c r="H89" s="22" t="inlineStr">
+        <is>
+          <t>泰國首座正統美式 Outlet！匯聚 Burberry、Coach、Nike 等國際名牌與知名精品折扣，回國前血拼勝地。</t>
+        </is>
+      </c>
+      <c r="I89" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+近機場適合最後一天採買</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="32" customHeight="1">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>V3-01</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D90" s="20" t="inlineStr">
+        <is>
+          <t>Samantao Heritage Coffee
+三曼陶傳統咖啡</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>市中心・Chit Lom 旁
+(Nai Lert Park 運河畔)</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>影片3: Amber Lee</t>
+        </is>
+      </c>
+      <c r="G90" s="21" t="inlineStr">
+        <is>
+          <t>00:32</t>
+        </is>
+      </c>
+      <c r="H90" s="22" t="inlineStr">
+        <is>
+          <t>隱身市中心奈樂花園的古風木屋傳統水岸咖啡！摩天樓環繞中的隱世綠洲，泰式黑咖啡、煎蛋吐司。</t>
+        </is>
+      </c>
+      <c r="I90" s="22" t="inlineStr">
+        <is>
+          <t>07:00–17:00
+氣氛悠閒環境清幽</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1">
+      <c r="A91" s="18" t="inlineStr">
+        <is>
+          <t>V3-02</t>
+        </is>
+      </c>
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D91" s="20" t="inlineStr">
+        <is>
+          <t>Balcony Cream Tea
+台灣茶冰淇淋概念店</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="inlineStr">
+        <is>
+          <t>市中心秘境商務小巷</t>
+        </is>
+      </c>
+      <c r="F91" s="18" t="inlineStr">
+        <is>
+          <t>影片3: Amber Lee</t>
+        </is>
+      </c>
+      <c r="G91" s="21" t="inlineStr">
+        <is>
+          <t>04:48</t>
+        </is>
+      </c>
+      <c r="H91" s="22" t="inlineStr">
+        <is>
+          <t>超人氣冰淇淋品牌 Guss Damn Good 旗下隱藏概念店！以不同濃度台灣高山烏龍、四季春、金萱製成頂級茶冰淇淋。</t>
+        </is>
+      </c>
+      <c r="I91" s="22" t="inlineStr">
+        <is>
+          <t>10:00–18:00
+茶香濃郁甜品控必吃</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="18" t="inlineStr">
+        <is>
+          <t>V3-03</t>
+        </is>
+      </c>
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>購物</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D92" s="20" t="inlineStr">
+        <is>
+          <t>Mitr 暹羅廣場旗艦店
+Mitr Flagship Store</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="inlineStr">
+        <is>
+          <t>暹羅廣場・Siam Square Soi 2</t>
+        </is>
+      </c>
+      <c r="F92" s="18" t="inlineStr">
+        <is>
+          <t>影片3: Amber Lee</t>
+        </is>
+      </c>
+      <c r="G92" s="21" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="H92" s="22" t="inlineStr">
+        <is>
+          <t>泰國超人氣設計師女裝品牌旗艦店（共三層樓）！法式泰系少女風、優質度假風亞麻襯衫、貝殼鈕扣洋裝與男女選品。</t>
+        </is>
+      </c>
+      <c r="I92" s="22" t="inlineStr">
+        <is>
+          <t>10:30–21:00
+泰國質感設計女裝必逛</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="32" customHeight="1">
+      <c r="A93" s="18" t="inlineStr">
+        <is>
+          <t>V4-01</t>
+        </is>
+      </c>
+      <c r="B93" s="18" t="inlineStr">
+        <is>
+          <t>住宿</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D93" s="20" t="inlineStr">
+        <is>
+          <t>VELA be Bangkok Siam
+曼谷暹羅維拉貝飯店</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="inlineStr">
+        <is>
+          <t>暹羅商圈・National Stadium
+(BTS 體育館站 3分鐘)</t>
+        </is>
+      </c>
+      <c r="F93" s="18" t="inlineStr">
+        <is>
+          <t>影片4: 美食猛男</t>
+        </is>
+      </c>
+      <c r="G93" s="21" t="inlineStr">
+        <is>
+          <t>00:20</t>
+        </is>
+      </c>
+      <c r="H93" s="22" t="inlineStr">
+        <is>
+          <t>暹羅商圈巷弄平價高質感設計旅宿，擁有露天水岸游泳池，客製單點現做精緻熱食早餐，價格非常實惠。</t>
+        </is>
+      </c>
+      <c r="I93" s="22" t="inlineStr">
+        <is>
+          <t>高 CP 值泳池飯店</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="18" t="inlineStr">
+        <is>
+          <t>V4-02</t>
+        </is>
+      </c>
+      <c r="B94" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D94" s="20" t="inlineStr">
+        <is>
+          <t>Café Dior 曼谷迪奧精品下午茶
+Café Dior Bangkok</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="inlineStr">
+        <is>
+          <t>市中心頂級精品百貨</t>
+        </is>
+      </c>
+      <c r="F94" s="18" t="inlineStr">
+        <is>
+          <t>影片4: 美食猛男</t>
+        </is>
+      </c>
+      <c r="G94" s="21" t="inlineStr">
+        <is>
+          <t>02:14</t>
+        </is>
+      </c>
+      <c r="H94" s="22" t="inlineStr">
+        <is>
+          <t>Dior 打造之頂級精品貴婦下午茶，精緻法式甜點雕花與尊榮環境服務。</t>
+        </is>
+      </c>
+      <c r="I94" s="22" t="inlineStr">
+        <is>
+          <t>10:00–20:00
+奢華精品打卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="18" t="inlineStr">
+        <is>
+          <t>V4-03</t>
+        </is>
+      </c>
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D95" s="20" t="inlineStr">
+        <is>
+          <t>Café Louis Vuitton &amp; LV The Place
+曼谷 LV 概念展覽與咖啡館</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="inlineStr">
+        <is>
+          <t>奇隆・Gaysorn Amarin
+(BTS Chit Lom 站直通)</t>
+        </is>
+      </c>
+      <c r="F95" s="18" t="inlineStr">
+        <is>
+          <t>影片4: 美食猛男</t>
+        </is>
+      </c>
+      <c r="G95" s="21" t="inlineStr">
+        <is>
+          <t>02:57</t>
+        </is>
+      </c>
+      <c r="H95" s="22" t="inlineStr">
+        <is>
+          <t>LV 曼谷全新概念地標！結合沉浸式品牌歷史光影展覽、名廚操刀精品咖啡館與旗艦購物空間。</t>
+        </is>
+      </c>
+      <c r="I95" s="22" t="inlineStr">
+        <is>
+          <t>10:00–20:00
+展覽需事先於官網預約</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="32" customHeight="1">
+      <c r="A96" s="18" t="inlineStr">
+        <is>
+          <t>V4-04</t>
+        </is>
+      </c>
+      <c r="B96" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D96" s="20" t="inlineStr">
+        <is>
+          <t>暹羅海洋世界
+Sea Life Bangkok Ocean World</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="inlineStr">
+        <is>
+          <t>暹羅・Siam Paragon B1
+(BTS Siam 站直通)</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>影片4: 美食猛男</t>
+        </is>
+      </c>
+      <c r="G96" s="21" t="inlineStr">
+        <is>
+          <t>04:13</t>
+        </is>
+      </c>
+      <c r="H96" s="22" t="inlineStr">
+        <is>
+          <t>東南亞最大室內水族館！擁有 270 度壯觀玻璃海底隧道、企鵝館、水獺餵食秀與玻璃底遊船。</t>
+        </is>
+      </c>
+      <c r="I96" s="22" t="inlineStr">
+        <is>
+          <t>10:00–20:00
+雨天及親子首選景點</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="18" t="inlineStr">
+        <is>
+          <t>V4-05</t>
+        </is>
+      </c>
+      <c r="B97" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D97" s="20" t="inlineStr">
+        <is>
+          <t>曼谷杜莎夫人蠟像館
+Madame Tussauds Bangkok</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="inlineStr">
+        <is>
+          <t>暹羅・Siam Discovery 4F
+(BTS Siam 站直通)</t>
+        </is>
+      </c>
+      <c r="F97" s="18" t="inlineStr">
+        <is>
+          <t>影片4: 美食猛男</t>
+        </is>
+      </c>
+      <c r="G97" s="21" t="inlineStr">
+        <is>
+          <t>05:16</t>
+        </is>
+      </c>
+      <c r="H97" s="22" t="inlineStr">
+        <is>
+          <t>世界知名蠟像館，匯集好萊塢巨星、各國政要、超級英雄、世界體育巨星等逼真等身蠟像。</t>
+        </is>
+      </c>
+      <c r="I97" s="22" t="inlineStr">
+        <is>
+          <t>10:00–20:00
+可與水族館購買聯票</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" s="18" t="inlineStr">
+        <is>
+          <t>V4-06</t>
+        </is>
+      </c>
+      <c r="B98" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>NAMA 日式海鮮吃到飽
+NAMA Japanese and Seafood</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr">
+        <is>
+          <t>市中心・CentralWorld 24F
+(Centara Grand 飯店 24 樓)</t>
+        </is>
+      </c>
+      <c r="F98" s="18" t="inlineStr">
+        <is>
+          <t>影片4: 美食猛男</t>
+        </is>
+      </c>
+      <c r="G98" s="21" t="inlineStr">
+        <is>
+          <t>06:14</t>
+        </is>
+      </c>
+      <c r="H98" s="22" t="inlineStr">
+        <is>
+          <t>高空日式海鮮百匯吃到飽！現開生蠔、巨大烤大頭蝦、生魚片刺身、炙燒和牛握壽司與哈根達斯無限享用。</t>
+        </is>
+      </c>
+      <c r="I98" s="22" t="inlineStr">
+        <is>
+          <t>午餐/晚餐時段
+高空景觀視野棒</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="32" customHeight="1">
+      <c r="A99" s="18" t="inlineStr">
+        <is>
+          <t>V5-01</t>
+        </is>
+      </c>
+      <c r="B99" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D99" s="20" t="inlineStr">
+        <is>
+          <t>小市場（塔拉諾伊文青巷）
+Talat Noi</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="inlineStr">
+        <is>
+          <t>老城區・Charoen Krung 巷弄
+(近 MRT 龍蓮寺站 / 華藍蓬站)</t>
+        </is>
+      </c>
+      <c r="F99" s="18" t="inlineStr">
+        <is>
+          <t>影片5: 屠潔</t>
+        </is>
+      </c>
+      <c r="G99" s="21" t="inlineStr">
+        <is>
+          <t>03:19</t>
+        </is>
+      </c>
+      <c r="H99" s="22" t="inlineStr">
+        <is>
+          <t>曼谷古老華人街區！百年老街牆面彩繪塗鴉壁畫、中古汽車廢鐵雕塑裝飾、老中藥行改建老宅咖啡館。</t>
+        </is>
+      </c>
+      <c r="I99" s="22" t="inlineStr">
+        <is>
+          <t>全天開放
+文青老街漫步</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="32" customHeight="1">
+      <c r="A100" s="18" t="inlineStr">
+        <is>
+          <t>V5-02</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D100" s="20" t="inlineStr">
+        <is>
+          <t>金佛寺
+Wat Traimit (Temple of Golden Buddha)</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
+        <is>
+          <t>唐人街起點
+(MRT 華藍蓬站 5分鐘)</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="inlineStr">
+        <is>
+          <t>影片5: 屠潔</t>
+        </is>
+      </c>
+      <c r="G100" s="21" t="inlineStr">
+        <is>
+          <t>04:39</t>
+        </is>
+      </c>
+      <c r="H100" s="22" t="inlineStr">
+        <is>
+          <t>曼谷唐人街重要象徵！供奉重達 5.5 噸、全世界最大的純金鑄造素可泰金坐佛，極具震撼力。</t>
+        </is>
+      </c>
+      <c r="I100" s="22" t="inlineStr">
+        <is>
+          <t>08:00–17:00
+門票約 100 銖</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1">
+      <c r="A101" s="18" t="inlineStr">
+        <is>
+          <t>V5-03</t>
+        </is>
+      </c>
+      <c r="B101" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D101" s="20" t="inlineStr">
+        <is>
+          <t>三頭神象博物館
+The Erawan Museum</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="inlineStr">
+        <is>
+          <t>北欖府・Samut Prakan
+(BTS Chang Erawan 站 8分鐘)</t>
+        </is>
+      </c>
+      <c r="F101" s="18" t="inlineStr">
+        <is>
+          <t>影片5: 屠潔</t>
+        </is>
+      </c>
+      <c r="G101" s="21" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="H101" s="22" t="inlineStr">
+        <is>
+          <t>重達 250 噸青銅三頭巨神象高聳於粉紅宮殿上！殿內雙螺旋雕花天梯與華麗彩繪玻璃圓頂，美拍視覺天花板。</t>
+        </is>
+      </c>
+      <c r="I101" s="22" t="inlineStr">
+        <is>
+          <t>09:00–18:00
+門票約 400 銖 (線上預訂較省)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="32" customHeight="1">
+      <c r="A102" s="18" t="inlineStr">
+        <is>
+          <t>V5-04</t>
+        </is>
+      </c>
+      <c r="B102" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>Sky Beach 78樓高空露天酒吧
+Sky Beach Bangkok</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t>王權大京都大廈 78 樓
+(BTS Chong Nonsi 站直通)</t>
+        </is>
+      </c>
+      <c r="F102" s="18" t="inlineStr">
+        <is>
+          <t>影片5: 屠潔</t>
+        </is>
+      </c>
+      <c r="G102" s="21" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="H102" s="22" t="inlineStr">
+        <is>
+          <t>曼谷最高 78 樓頂層露天黃色摩登酒吧！吹著涼風俯瞰天使之城 360 度無死角百萬日落與星空夜景。</t>
+        </is>
+      </c>
+      <c r="I102" s="22" t="inlineStr">
+        <is>
+          <t>10:00–00:00
+需持觀景台票或點飲料</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="32" customHeight="1">
+      <c r="A103" s="18" t="inlineStr">
+        <is>
+          <t>V5-05</t>
+        </is>
+      </c>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D103" s="20" t="inlineStr">
+        <is>
+          <t>After the Rain Coffee &amp; Gallery
+雨林划船咖啡廳</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="inlineStr">
+        <is>
+          <t>佛統府・Sam Phran
+(曼谷市區車程約40分鐘)</t>
+        </is>
+      </c>
+      <c r="F103" s="18" t="inlineStr">
+        <is>
+          <t>影片5: 屠潔</t>
+        </is>
+      </c>
+      <c r="G103" s="21" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="H103" s="22" t="inlineStr">
+        <is>
+          <t>熱帶雨林綠意運河咖啡館！可一邊悠閒享用下午茶，一邊親自划木舟穿梭在兩側滿滿熱帶果樹運河中拍照。</t>
+        </is>
+      </c>
+      <c r="I103" s="22" t="inlineStr">
+        <is>
+          <t>08:30–18:30 (週一休)
+近郊網美划船名店</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="18" t="inlineStr">
+        <is>
+          <t>V5-06</t>
+        </is>
+      </c>
+      <c r="B104" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D104" s="20" t="inlineStr">
+        <is>
+          <t>Moo Yoo Rose House 湖畔玫瑰咖啡
+Moo Yoo Rose House</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="inlineStr">
+        <is>
+          <t>佛統府・Bang Len</t>
+        </is>
+      </c>
+      <c r="F104" s="18" t="inlineStr">
+        <is>
+          <t>影片5: 屠潔</t>
+        </is>
+      </c>
+      <c r="G104" s="21" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="H104" s="22" t="inlineStr">
+        <is>
+          <t>湖畔純白極簡風莊園咖啡廳！大片全景落地玻璃窗倒映湖景，專賣排隊現烤法式可頌、可朗芙與玫瑰系甜品。</t>
+        </is>
+      </c>
+      <c r="I104" s="22" t="inlineStr">
+        <is>
+          <t>09:00–18:00
+純白極簡好拍照</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="18" t="inlineStr">
+        <is>
+          <t>V6-01</t>
+        </is>
+      </c>
+      <c r="B105" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C105" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D105" s="20" t="inlineStr">
+        <is>
+          <t>Racha Nuea Toon 牛肉湯之王
+Racha Nuea Toon (ราชาเนื้อตุ๋น)</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="inlineStr">
+        <is>
+          <t>曼谷老牌牛肉湯
+Sukhumvit 周邊</t>
+        </is>
+      </c>
+      <c r="F105" s="18" t="inlineStr">
+        <is>
+          <t>影片6: 戴妮塔</t>
+        </is>
+      </c>
+      <c r="G105" s="21" t="inlineStr">
+        <is>
+          <t>00:50</t>
+        </is>
+      </c>
+      <c r="H105" s="22" t="inlineStr">
+        <is>
+          <t>曼谷在地司機老饕認證牛肉湯第一名！炭火大鍋長時間熬煮，牛腩軟嫩化口、牛筋軟Q，藥膳大骨高湯無敵香濃。</t>
+        </is>
+      </c>
+      <c r="I105" s="22" t="inlineStr">
+        <is>
+          <t>08:00–23:00
+愛吃牛肉麵老饕必吃</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="32" customHeight="1">
+      <c r="A106" s="18" t="inlineStr">
+        <is>
+          <t>V6-02</t>
+        </is>
+      </c>
+      <c r="B106" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C106" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D106" s="20" t="inlineStr">
+        <is>
+          <t>桌金 Toh-Kim 泰國海南雞飯
+โต๊ะกิม ข้าวมันไก่</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="inlineStr">
+        <is>
+          <t>曼谷隱藏老饕店</t>
+        </is>
+      </c>
+      <c r="F106" s="18" t="inlineStr">
+        <is>
+          <t>影片6: 戴妮塔</t>
+        </is>
+      </c>
+      <c r="G106" s="21" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="H106" s="22" t="inlineStr">
+        <is>
+          <t>老饕私藏極嫩海南雞飯！雞皮滑嫩如果凍，雞胸雞腿爆汁軟嫩，搭配顆粒分明雞油香飯與微辣薑蒜沾醬。</t>
+        </is>
+      </c>
+      <c r="I106" s="22" t="inlineStr">
+        <is>
+          <t>10:00–21:00
+海南雞肉質極佳</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="32" customHeight="1">
+      <c r="A107" s="18" t="inlineStr">
+        <is>
+          <t>V6-03</t>
+        </is>
+      </c>
+      <c r="B107" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C107" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D107" s="20" t="inlineStr">
+        <is>
+          <t>EPIA Sukhumvit 89 海鮮銅鍋
+EPIA Sukhumvit 89</t>
+        </is>
+      </c>
+      <c r="E107" s="18" t="inlineStr">
+        <is>
+          <t>素坤逸・Sukhumvit 89 巷
+(BTS Bang Chak 站旁)</t>
+        </is>
+      </c>
+      <c r="F107" s="18" t="inlineStr">
+        <is>
+          <t>影片6: 戴妮塔</t>
+        </is>
+      </c>
+      <c r="G107" s="21" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="H107" s="22" t="inlineStr">
+        <is>
+          <t>泰式金屬雙耳銅鍋海鮮冬陰功！爆量大頭蝦、鮮美魷魚與鮮菇，湯頭酸辣甘醇，亦有炭火熱烤肉盤。</t>
+        </is>
+      </c>
+      <c r="I107" s="22" t="inlineStr">
+        <is>
+          <t>12:00–22:00
+冬陰功濃郁海鮮足</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="32" customHeight="1">
+      <c r="A108" s="18" t="inlineStr">
+        <is>
+          <t>V6-04</t>
+        </is>
+      </c>
+      <c r="B108" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>GAPOW TAPAE 打拋豬專賣天花板
+กะเพราตาแป๊ะ</t>
+        </is>
+      </c>
+      <c r="E108" s="18" t="inlineStr">
+        <is>
+          <t>素坤逸・Asok / Phrom Phong 間</t>
+        </is>
+      </c>
+      <c r="F108" s="18" t="inlineStr">
+        <is>
+          <t>影片6: 戴妮塔</t>
+        </is>
+      </c>
+      <c r="G108" s="21" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="H108" s="22" t="inlineStr">
+        <is>
+          <t>打拋豬天花板！純粹打拋葉與香料大火乾炒豬肉碎（無玉米筍長豆），辣度自由挑選，配半熟外酥煎鴨蛋。</t>
+        </is>
+      </c>
+      <c r="I108" s="22" t="inlineStr">
+        <is>
+          <t>09:30–15:00 / 16:00–20:00
+正統泰式打拋葉乾炒</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="18" t="inlineStr">
+        <is>
+          <t>V6-05</t>
+        </is>
+      </c>
+      <c r="B109" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C109" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D109" s="20" t="inlineStr">
+        <is>
+          <t>Ros Mue Mae 媽媽的手藝 (隱藏無名咖喱蝦)
+รสมือแม่ (朱拉50巷)</t>
+        </is>
+      </c>
+      <c r="E109" s="18" t="inlineStr">
+        <is>
+          <t>山燕・Sam Yan / 朱拉50巷
+(MRT Sam Yan 站)</t>
+        </is>
+      </c>
+      <c r="F109" s="18" t="inlineStr">
+        <is>
+          <t>影片6: 戴妮塔</t>
+        </is>
+      </c>
+      <c r="G109" s="21" t="inlineStr">
+        <is>
+          <t>26:55</t>
+        </is>
+      </c>
+      <c r="H109" s="22" t="inlineStr">
+        <is>
+          <t>朱拉50巷旁老饕私房無招牌熱炒！招牌「黃金滑蛋濃咖哩炒大蝦」滑嫩無比爆下飯，脆皮五花豬肉與酸辣排骨湯一流。</t>
+        </is>
+      </c>
+      <c r="I109" s="22" t="inlineStr">
+        <is>
+          <t>15:00–19:30 (週末休)
+在地人才知道的寶藏店</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="18" t="inlineStr">
+        <is>
+          <t>V7-01</t>
+        </is>
+      </c>
+      <c r="B110" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D110" s="20" t="inlineStr">
+        <is>
+          <t>Tha Tien Pier 塔天碼頭
+Tha Tien Pier</t>
+        </is>
+      </c>
+      <c r="E110" s="18" t="inlineStr">
+        <is>
+          <t>昭披耶河畔
+(臥佛寺正後方碼頭)</t>
+        </is>
+      </c>
+      <c r="F110" s="18" t="inlineStr">
+        <is>
+          <t>影片7: 喵兔自由行</t>
+        </is>
+      </c>
+      <c r="G110" s="21" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="H110" s="22" t="inlineStr">
+        <is>
+          <t>橫渡湄南河經典碼頭！只要花費 5 泰銖即可搭乘接駁小渡輪橫渡河面抵達對岸鄭王廟，沿途可拍佛寺全景。</t>
+        </is>
+      </c>
+      <c r="I110" s="22" t="inlineStr">
+        <is>
+          <t>05:00–19:00
+橫渡只要 5 銖</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="32" customHeight="1">
+      <c r="A111" s="18" t="inlineStr">
+        <is>
+          <t>V7-02</t>
+        </is>
+      </c>
+      <c r="B111" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C111" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D111" s="20" t="inlineStr">
+        <is>
+          <t>席隆周邊夜市散步
+Silom Night Market / Patpong</t>
+        </is>
+      </c>
+      <c r="E111" s="18" t="inlineStr">
+        <is>
+          <t>席隆・Silom
+(BTS Sala Daeng 站)</t>
+        </is>
+      </c>
+      <c r="F111" s="18" t="inlineStr">
+        <is>
+          <t>影片7: 喵兔自由行</t>
+        </is>
+      </c>
+      <c r="G111" s="21" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="H111" s="22" t="inlineStr">
+        <is>
+          <t>席隆商業區夜間熱鬧夜市散步動線，品嘗各式路邊泰式甜品、椰子冰淇淋、炸香蕉與烤肉串。</t>
+        </is>
+      </c>
+      <c r="I111" s="22" t="inlineStr">
+        <is>
+          <t>18:00–00:00
+交通便利熱鬧市區</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="32" customHeight="1">
+      <c r="A112" s="18" t="inlineStr">
+        <is>
+          <t>V8-01</t>
+        </is>
+      </c>
+      <c r="B112" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D112" s="20" t="inlineStr">
+        <is>
+          <t>Cloud 11 未來感生活新地標商場
+Cloud 11 Bangkok</t>
+        </is>
+      </c>
+      <c r="E112" s="18" t="inlineStr">
+        <is>
+          <t>素坤逸・Punnawithi
+(BTS Punnawithi 站直通天橋)</t>
+        </is>
+      </c>
+      <c r="F112" s="18" t="inlineStr">
+        <is>
+          <t>影片8: myKleb</t>
+        </is>
+      </c>
+      <c r="G112" s="21" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="H112" s="22" t="inlineStr">
+        <is>
+          <t>曼谷最新落成未來感智慧生活商場！集結創新科技辦公室、文創工藝工作室、智慧飯店、綠意中庭與美食空間。</t>
+        </is>
+      </c>
+      <c r="I112" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+最新落成新地標</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="32" customHeight="1">
+      <c r="A113" s="18" t="inlineStr">
+        <is>
+          <t>V8-02</t>
+        </is>
+      </c>
+      <c r="B113" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C113" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D113" s="20" t="inlineStr">
+        <is>
+          <t>Cloud 11 5樓超大型空中花園草地
+5F Rooftop Lawn &amp; Sky Garden</t>
+        </is>
+      </c>
+      <c r="E113" s="18" t="inlineStr">
+        <is>
+          <t>Cloud 11 商場 5 樓
+(BTS Punnawithi 站)</t>
+        </is>
+      </c>
+      <c r="F113" s="18" t="inlineStr">
+        <is>
+          <t>影片8: myKleb</t>
+        </is>
+      </c>
+      <c r="G113" s="21" t="inlineStr">
+        <is>
+          <t>05:32</t>
+        </is>
+      </c>
+      <c r="H113" s="22" t="inlineStr">
+        <is>
+          <t>曼谷市中心罕見遼闊頂樓戶外大草坪！視野開闊無遮蔽、微風徐徐，設有噴水池、立食野餐桌，常態舉辦藝文活動。</t>
+        </is>
+      </c>
+      <c r="I113" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+市中心野餐吹風打卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="32" customHeight="1">
+      <c r="A114" s="18" t="inlineStr">
+        <is>
+          <t>V8-03</t>
+        </is>
+      </c>
+      <c r="B114" s="18" t="inlineStr">
+        <is>
+          <t>住宿</t>
+        </is>
+      </c>
+      <c r="C114" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D114" s="20" t="inlineStr">
+        <is>
+          <t>YOTEL Bangkok
+曼谷尤特爾智慧潮流飯店</t>
+        </is>
+      </c>
+      <c r="E114" s="18" t="inlineStr">
+        <is>
+          <t>Cloud 11 建築群內
+(BTS Punnawithi 站)</t>
+        </is>
+      </c>
+      <c r="F114" s="18" t="inlineStr">
+        <is>
+          <t>影片8: myKleb</t>
+        </is>
+      </c>
+      <c r="G114" s="21" t="inlineStr">
+        <is>
+          <t>05:56</t>
+        </is>
+      </c>
+      <c r="H114" s="22" t="inlineStr">
+        <is>
+          <t>全球知名英國智慧潮流設計旅店！主打無接觸智慧入住設施、景觀客房與現代社群交誼空間，科技感十足。</t>
+        </is>
+      </c>
+      <c r="I114" s="22" t="inlineStr">
+        <is>
+          <t>最新落成智慧旅宿</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="32" customHeight="1">
+      <c r="A115" s="18" t="inlineStr">
+        <is>
+          <t>V8-04</t>
+        </is>
+      </c>
+      <c r="B115" s="18" t="inlineStr">
+        <is>
+          <t>景點</t>
+        </is>
+      </c>
+      <c r="C115" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D115" s="20" t="inlineStr">
+        <is>
+          <t>泰北藝術文化創意展覽區
+Cloud 11 Art &amp; Cultural Space</t>
+        </is>
+      </c>
+      <c r="E115" s="18" t="inlineStr">
+        <is>
+          <t>Cloud 11 商場 5 樓室內</t>
+        </is>
+      </c>
+      <c r="F115" s="18" t="inlineStr">
+        <is>
+          <t>影片8: myKleb</t>
+        </is>
+      </c>
+      <c r="G115" s="21" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="H115" s="22" t="inlineStr">
+        <is>
+          <t>展示泰北清邁清萊手作陶藝品、手工宣紙、天然蜂蜜與特色莊園咖啡豆，定期舉辦當代泰國藝術家特展。</t>
+        </is>
+      </c>
+      <c r="I115" s="22" t="inlineStr">
+        <is>
+          <t>10:00–20:00
+文創藝術愛好者必看</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="32" customHeight="1">
+      <c r="A116" s="18" t="inlineStr">
+        <is>
+          <t>V8-05</t>
+        </is>
+      </c>
+      <c r="B116" s="18" t="inlineStr">
+        <is>
+          <t>美食</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D116" s="20" t="inlineStr">
+        <is>
+          <t>theCOMMONS Cloud 11
+開放式挑高階梯庭園美食街</t>
+        </is>
+      </c>
+      <c r="E116" s="18" t="inlineStr">
+        <is>
+          <t>Cloud 11 商場低樓層</t>
+        </is>
+      </c>
+      <c r="F116" s="18" t="inlineStr">
+        <is>
+          <t>影片8: myKleb</t>
+        </is>
+      </c>
+      <c r="G116" s="21" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="H116" s="22" t="inlineStr">
+        <is>
+          <t>曼谷文青社群聚落 theCOMMONS 最新分館！標誌性自然採光階梯庭園與大吊扇，匯聚高品質咖啡、漢堡、塔可與起司冷肉盤。</t>
+        </is>
+      </c>
+      <c r="I116" s="22" t="inlineStr">
+        <is>
+          <t>10:00–22:00
+環境極為悠閒舒服</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId110"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/曼谷自由行心願清單.xlsx
+++ b/曼谷自由行心願清單.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -272,6 +272,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -372,9 +378,31 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -389,20 +417,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -417,20 +467,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -445,20 +517,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -473,20 +567,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -501,20 +617,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -529,20 +667,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -557,20 +717,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -585,20 +767,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -613,20 +817,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="10" name="Image 10" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -641,20 +867,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -669,20 +917,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -697,20 +967,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -725,20 +1017,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -753,20 +1067,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="15" name="Image 15" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -781,20 +1117,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -809,20 +1167,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -837,20 +1217,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -865,20 +1267,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -893,20 +1317,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -921,20 +1367,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -949,20 +1417,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -977,20 +1467,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1005,20 +1517,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1033,20 +1567,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1061,20 +1617,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1089,20 +1667,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1117,20 +1717,42 @@
     <ext cx="1047750" cy="685800"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="685800"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1161,6 +1783,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1186,6 +1811,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1211,6 +1839,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1236,6 +1867,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1261,6 +1895,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1286,6 +1923,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1311,6 +1951,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1336,6 +1979,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1361,6 +2007,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1386,6 +2035,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1411,6 +2063,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1436,6 +2091,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1461,6 +2119,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1486,6 +2147,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1511,6 +2175,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1536,6 +2203,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1561,6 +2231,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1586,6 +2259,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1611,6 +2287,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1636,6 +2315,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1661,6 +2343,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1686,6 +2371,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1711,6 +2399,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1736,6 +2427,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1761,6 +2455,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1786,6 +2483,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1811,6 +2511,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1836,6 +2539,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1861,6 +2567,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1886,6 +2595,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1911,6 +2623,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1936,6 +2651,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1961,6 +2679,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1986,6 +2707,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2011,6 +2735,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2036,6 +2763,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2061,6 +2791,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2086,6 +2819,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2111,6 +2847,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2136,6 +2875,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2161,6 +2903,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2186,6 +2931,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2211,6 +2959,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2236,6 +2987,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2261,6 +3015,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2286,6 +3043,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2311,6 +3071,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2336,6 +3099,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2361,6 +3127,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2386,6 +3155,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2411,6 +3183,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2436,6 +3211,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2461,6 +3239,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2486,6 +3267,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2511,6 +3295,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2536,6 +3323,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2561,6 +3351,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2586,6 +3379,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2611,6 +3407,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2636,6 +3435,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2661,6 +3463,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2686,6 +3491,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2711,6 +3519,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2736,6 +3547,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2761,6 +3575,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2786,6 +3603,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2811,6 +3631,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2836,6 +3659,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2861,6 +3687,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2886,6 +3715,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2911,6 +3743,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2936,6 +3771,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2961,6 +3799,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2986,6 +3827,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3011,6 +3855,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3036,6 +3883,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3061,6 +3911,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3086,6 +3939,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3111,6 +3967,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3136,6 +3995,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3161,6 +4023,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3186,6 +4051,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3211,6 +4079,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3236,6 +4107,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3261,6 +4135,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3286,6 +4163,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3311,6 +4191,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3336,6 +4219,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3361,6 +4247,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3386,6 +4275,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3411,6 +4303,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3436,6 +4331,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3461,6 +4359,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3486,6 +4387,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3511,6 +4415,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3536,6 +4443,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3561,6 +4471,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3586,6 +4499,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3611,6 +4527,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3636,6 +4555,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3661,6 +4583,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3686,6 +4611,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3711,6 +4639,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3736,6 +4667,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3761,6 +4695,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3786,6 +4723,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3811,6 +4751,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3836,6 +4779,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3861,6 +4807,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3886,6 +4835,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3911,6 +4863,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3936,6 +4891,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3961,6 +4919,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3986,6 +4947,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4011,6 +4975,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4036,6 +5003,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4061,6 +5031,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4086,6 +5059,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4111,6 +5087,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4136,6 +5115,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4161,6 +5143,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4186,6 +5171,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4211,6 +5199,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4236,6 +5227,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4261,6 +5255,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4286,6 +5283,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4311,6 +5311,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4336,6 +5339,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4361,6 +5367,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4386,6 +5395,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4411,6 +5423,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4436,6 +5451,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4461,6 +5479,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4486,6 +5507,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4511,6 +5535,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4536,6 +5563,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4561,6 +5591,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4586,6 +5619,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4611,6 +5647,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4636,6 +5675,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4661,6 +5703,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4686,6 +5731,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4711,6 +5759,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4736,6 +5787,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4761,6 +5815,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4786,6 +5843,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4811,6 +5871,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4836,6 +5899,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4861,6 +5927,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4886,6 +5955,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4911,6 +5983,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4936,6 +6011,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4961,6 +6039,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4986,6 +6067,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5011,6 +6095,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5036,6 +6123,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5061,6 +6151,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5086,6 +6179,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5111,6 +6207,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5136,6 +6235,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5161,6 +6263,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5186,6 +6291,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5211,6 +6319,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5236,6 +6347,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5261,6 +6375,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5286,6 +6403,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5311,6 +6431,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5336,6 +6459,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5361,6 +6487,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5386,6 +6515,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5411,6 +6543,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5436,6 +6571,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5461,6 +6599,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5486,6 +6627,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5511,6 +6655,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5536,6 +6683,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5561,6 +6711,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5586,6 +6739,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5611,6 +6767,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5636,6 +6795,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5661,6 +6823,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5686,6 +6851,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5711,6 +6879,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5736,6 +6907,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5761,6 +6935,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5786,6 +6963,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5811,6 +6991,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5836,6 +7019,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5861,6 +7047,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5886,6 +7075,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5911,6 +7103,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5936,6 +7131,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5961,6 +7159,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5986,6 +7187,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6011,6 +7215,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6036,6 +7243,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6061,6 +7271,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6086,6 +7299,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6111,6 +7327,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6136,6 +7355,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6161,6 +7383,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6186,6 +7411,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6211,6 +7439,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6236,6 +7467,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6261,6 +7495,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6286,6 +7523,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6311,6 +7551,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6336,6 +7579,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6361,6 +7607,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6386,6 +7635,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6411,6 +7663,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6436,6 +7691,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6461,6 +7719,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6486,6 +7747,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6511,6 +7775,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6536,6 +7803,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6561,6 +7831,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6586,6 +7859,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6611,6 +7887,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6636,6 +7915,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6932,7 +8214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6941,7 +8223,8 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="35" customHeight="1">
@@ -6950,6 +8233,7 @@
           <t>🇹🇭 曼谷自由行心願清單</t>
         </is>
       </c>
+      <c r="H1" s="10" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -6982,9 +8266,14 @@
           <t>備註</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>圖片</t>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>圖片 1 (環境/外觀/風景)</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>圖片 2 (特色/餐點/設施)</t>
         </is>
       </c>
     </row>
@@ -7020,6 +8309,7 @@
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="25" t="n"/>
     </row>
     <row r="4" ht="70" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -7053,6 +8343,7 @@
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="25" t="n"/>
     </row>
     <row r="5" ht="70" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -7086,6 +8377,7 @@
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="25" t="n"/>
     </row>
     <row r="6" ht="70" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -7119,6 +8411,7 @@
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="25" t="n"/>
     </row>
     <row r="7" ht="70" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -7152,6 +8445,7 @@
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="25" t="n"/>
     </row>
     <row r="8" ht="70" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
@@ -7185,6 +8479,7 @@
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr"/>
+      <c r="H8" s="25" t="n"/>
     </row>
     <row r="9" ht="70" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -7218,6 +8513,7 @@
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="25" t="n"/>
     </row>
     <row r="10" ht="70" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -7251,6 +8547,7 @@
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr"/>
+      <c r="H10" s="25" t="n"/>
     </row>
     <row r="11" ht="70" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -7284,6 +8581,7 @@
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="25" t="n"/>
     </row>
     <row r="12" ht="70" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -7317,6 +8615,7 @@
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr"/>
+      <c r="H12" s="25" t="n"/>
     </row>
     <row r="13" ht="70" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -7350,6 +8649,7 @@
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="25" t="n"/>
     </row>
     <row r="14" ht="70" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
@@ -7383,6 +8683,7 @@
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr"/>
+      <c r="H14" s="25" t="n"/>
     </row>
     <row r="15" ht="70" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -7416,6 +8717,7 @@
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr"/>
+      <c r="H15" s="25" t="n"/>
     </row>
     <row r="16" ht="70" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -7449,6 +8751,7 @@
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr"/>
+      <c r="H16" s="25" t="n"/>
     </row>
     <row r="17" ht="70" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -7482,6 +8785,7 @@
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr"/>
+      <c r="H17" s="25" t="n"/>
     </row>
     <row r="18" ht="70" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -7515,6 +8819,7 @@
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr"/>
+      <c r="H18" s="25" t="n"/>
     </row>
     <row r="19" ht="70" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -7548,6 +8853,7 @@
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="25" t="n"/>
     </row>
     <row r="20" ht="70" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
@@ -7581,6 +8887,7 @@
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr"/>
+      <c r="H20" s="25" t="n"/>
     </row>
     <row r="21" ht="70" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -7614,6 +8921,7 @@
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="25" t="n"/>
     </row>
     <row r="22" ht="70" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -7647,6 +8955,7 @@
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr"/>
+      <c r="H22" s="25" t="n"/>
     </row>
     <row r="23" ht="70" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -7680,6 +8989,7 @@
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="25" t="n"/>
     </row>
     <row r="24" ht="70" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -7713,6 +9023,7 @@
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr"/>
+      <c r="H24" s="25" t="n"/>
     </row>
     <row r="25" ht="70" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -7746,6 +9057,7 @@
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="25" t="n"/>
     </row>
     <row r="26" ht="70" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -7779,6 +9091,7 @@
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr"/>
+      <c r="H26" s="25" t="n"/>
     </row>
     <row r="27" ht="70" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -7812,6 +9125,7 @@
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="25" t="n"/>
     </row>
     <row r="28" ht="70" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
@@ -7845,6 +9159,7 @@
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr"/>
+      <c r="H28" s="25" t="n"/>
     </row>
     <row r="29" ht="70" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -7878,6 +9193,7 @@
         </is>
       </c>
       <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="25" t="n"/>
     </row>
     <row r="30" ht="70" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
@@ -7911,10 +9227,11 @@
         </is>
       </c>
       <c r="G30" s="8" t="inlineStr"/>
+      <c r="H30" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
@@ -8527,15 +9844,15 @@
           <t>🇹🇭 曼谷自由行 影音參考影片提及地點全攻略 (含米其林指南推薦專區)</t>
         </is>
       </c>
-      <c r="B1" s="10" t="n"/>
-      <c r="C1" s="10" t="n"/>
-      <c r="D1" s="10" t="n"/>
-      <c r="E1" s="10" t="n"/>
-      <c r="F1" s="10" t="n"/>
-      <c r="G1" s="10" t="n"/>
-      <c r="H1" s="10" t="n"/>
-      <c r="I1" s="10" t="n"/>
-      <c r="J1" s="10" t="n"/>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+      <c r="H1" s="13" t="n"/>
+      <c r="I1" s="13" t="n"/>
+      <c r="J1" s="14" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
@@ -8543,15 +9860,15 @@
           <t>🏆 【精選專區】影音推薦「米其林指南」必吃美食清單（13處必比登推薦與星級入選）</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
+      <c r="B2" s="13" t="n"/>
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="13" t="n"/>
+      <c r="F2" s="13" t="n"/>
+      <c r="G2" s="13" t="n"/>
+      <c r="H2" s="13" t="n"/>
+      <c r="I2" s="13" t="n"/>
+      <c r="J2" s="14" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
@@ -9235,15 +10552,15 @@
           <t>🎬 【完整收錄】8 部 YouTube 攻略影片逐項地點與精確時間軸總覽（美食 / 景點 / 住宿 / 購物）</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="10" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="10" t="n"/>
-      <c r="I18" s="10" t="n"/>
-      <c r="J18" s="10" t="n"/>
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
+      <c r="G18" s="13" t="n"/>
+      <c r="H18" s="13" t="n"/>
+      <c r="I18" s="13" t="n"/>
+      <c r="J18" s="14" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="17" t="inlineStr">
